--- a/reports/excel/E2E_Report.xlsx
+++ b/reports/excel/E2E_Report.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2887" uniqueCount="850">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2887" uniqueCount="852">
   <si>
     <t>📊 E2E REPORT - AUTOMATION EXECUTION SUMMARY</t>
   </si>
@@ -97,7 +97,10 @@
     <t>PASSED</t>
   </si>
   <si>
-    <t>2026-08-20 03:51:22</t>
+    <t>2026-08-20 04:37:21</t>
+  </si>
+  <si>
+    <t>0.01s</t>
   </si>
   <si>
     <t>TC-SEL-002</t>
@@ -403,9 +406,6 @@
     <t>Dynamic Crawler: Discover and index root page forms</t>
   </si>
   <si>
-    <t>0.01s</t>
-  </si>
-  <si>
     <t>TC-SEL-052</t>
   </si>
   <si>
@@ -442,10 +442,16 @@
     <t>Dynamic Crawler: Discover and index /roundup synthesis forms</t>
   </si>
   <si>
+    <t>0.06s</t>
+  </si>
+  <si>
     <t>TC-SEL-058</t>
   </si>
   <si>
     <t>Dynamic Crawler: Verify all discovered forms specify valid action URI</t>
+  </si>
+  <si>
+    <t>0.02s</t>
   </si>
   <si>
     <t>TC-SEL-059</t>
@@ -3351,18 +3357,18 @@
         <v>27</v>
       </c>
       <c r="H2" s="15" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="17" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B3" s="18" t="s">
         <v>23</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D3" s="20" t="s">
         <v>25</v>
@@ -3382,13 +3388,13 @@
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B4" s="13" t="s">
         <v>23</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D4" s="15" t="s">
         <v>25</v>
@@ -3408,13 +3414,13 @@
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="17" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B5" s="18" t="s">
         <v>23</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D5" s="20" t="s">
         <v>25</v>
@@ -3434,13 +3440,13 @@
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B6" s="13" t="s">
         <v>23</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D6" s="15" t="s">
         <v>25</v>
@@ -3460,13 +3466,13 @@
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="17" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B7" s="18" t="s">
         <v>23</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D7" s="20" t="s">
         <v>25</v>
@@ -3486,13 +3492,13 @@
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B8" s="13" t="s">
         <v>23</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D8" s="15" t="s">
         <v>25</v>
@@ -3512,13 +3518,13 @@
     </row>
     <row r="9" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B9" s="18" t="s">
         <v>23</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D9" s="20" t="s">
         <v>25</v>
@@ -3538,13 +3544,13 @@
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B10" s="13" t="s">
         <v>23</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D10" s="15" t="s">
         <v>25</v>
@@ -3564,13 +3570,13 @@
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="17" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B11" s="18" t="s">
         <v>23</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D11" s="20" t="s">
         <v>25</v>
@@ -3590,13 +3596,13 @@
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B12" s="13" t="s">
         <v>23</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D12" s="15" t="s">
         <v>25</v>
@@ -3611,18 +3617,18 @@
         <v>27</v>
       </c>
       <c r="H12" s="15" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="17" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B13" s="18" t="s">
         <v>23</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D13" s="20" t="s">
         <v>25</v>
@@ -3642,13 +3648,13 @@
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B14" s="13" t="s">
         <v>23</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D14" s="15" t="s">
         <v>25</v>
@@ -3668,13 +3674,13 @@
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="17" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B15" s="18" t="s">
         <v>23</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D15" s="20" t="s">
         <v>25</v>
@@ -3694,13 +3700,13 @@
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B16" s="13" t="s">
         <v>23</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D16" s="15" t="s">
         <v>25</v>
@@ -3720,13 +3726,13 @@
     </row>
     <row r="17" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="17" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B17" s="18" t="s">
         <v>23</v>
       </c>
       <c r="C17" s="19" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D17" s="20" t="s">
         <v>25</v>
@@ -3746,13 +3752,13 @@
     </row>
     <row r="18" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B18" s="13" t="s">
         <v>23</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D18" s="15" t="s">
         <v>25</v>
@@ -3772,13 +3778,13 @@
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="17" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B19" s="18" t="s">
         <v>23</v>
       </c>
       <c r="C19" s="19" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D19" s="20" t="s">
         <v>25</v>
@@ -3798,13 +3804,13 @@
     </row>
     <row r="20" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="12" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B20" s="13" t="s">
         <v>23</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D20" s="15" t="s">
         <v>25</v>
@@ -3824,13 +3830,13 @@
     </row>
     <row r="21" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="17" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B21" s="18" t="s">
         <v>23</v>
       </c>
       <c r="C21" s="19" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D21" s="20" t="s">
         <v>25</v>
@@ -3850,13 +3856,13 @@
     </row>
     <row r="22" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="12" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B22" s="13" t="s">
         <v>23</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D22" s="15" t="s">
         <v>25</v>
@@ -3876,13 +3882,13 @@
     </row>
     <row r="23" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="17" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B23" s="18" t="s">
         <v>23</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D23" s="20" t="s">
         <v>25</v>
@@ -3902,13 +3908,13 @@
     </row>
     <row r="24" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B24" s="13" t="s">
         <v>23</v>
       </c>
       <c r="C24" s="14" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D24" s="15" t="s">
         <v>25</v>
@@ -3928,13 +3934,13 @@
     </row>
     <row r="25" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="17" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B25" s="18" t="s">
         <v>23</v>
       </c>
       <c r="C25" s="19" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D25" s="20" t="s">
         <v>25</v>
@@ -3954,13 +3960,13 @@
     </row>
     <row r="26" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="12" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B26" s="13" t="s">
         <v>23</v>
       </c>
       <c r="C26" s="14" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D26" s="15" t="s">
         <v>25</v>
@@ -3980,13 +3986,13 @@
     </row>
     <row r="27" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="17" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B27" s="18" t="s">
         <v>23</v>
       </c>
       <c r="C27" s="19" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D27" s="20" t="s">
         <v>25</v>
@@ -4006,13 +4012,13 @@
     </row>
     <row r="28" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="12" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B28" s="13" t="s">
         <v>23</v>
       </c>
       <c r="C28" s="14" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D28" s="15" t="s">
         <v>25</v>
@@ -4032,13 +4038,13 @@
     </row>
     <row r="29" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="17" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B29" s="18" t="s">
         <v>23</v>
       </c>
       <c r="C29" s="19" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D29" s="20" t="s">
         <v>25</v>
@@ -4058,13 +4064,13 @@
     </row>
     <row r="30" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="12" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B30" s="13" t="s">
         <v>23</v>
       </c>
       <c r="C30" s="14" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D30" s="15" t="s">
         <v>25</v>
@@ -4084,13 +4090,13 @@
     </row>
     <row r="31" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B31" s="18" t="s">
         <v>23</v>
       </c>
       <c r="C31" s="19" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D31" s="20" t="s">
         <v>25</v>
@@ -4110,13 +4116,13 @@
     </row>
     <row r="32" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="12" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B32" s="13" t="s">
         <v>23</v>
       </c>
       <c r="C32" s="14" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D32" s="15" t="s">
         <v>25</v>
@@ -4136,13 +4142,13 @@
     </row>
     <row r="33" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="17" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B33" s="18" t="s">
         <v>23</v>
       </c>
       <c r="C33" s="19" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D33" s="20" t="s">
         <v>25</v>
@@ -4162,13 +4168,13 @@
     </row>
     <row r="34" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="12" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B34" s="13" t="s">
         <v>23</v>
       </c>
       <c r="C34" s="14" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D34" s="15" t="s">
         <v>25</v>
@@ -4188,13 +4194,13 @@
     </row>
     <row r="35" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="17" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B35" s="18" t="s">
         <v>23</v>
       </c>
       <c r="C35" s="19" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D35" s="20" t="s">
         <v>25</v>
@@ -4214,13 +4220,13 @@
     </row>
     <row r="36" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="12" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B36" s="13" t="s">
         <v>23</v>
       </c>
       <c r="C36" s="14" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D36" s="15" t="s">
         <v>25</v>
@@ -4240,13 +4246,13 @@
     </row>
     <row r="37" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="17" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B37" s="18" t="s">
         <v>23</v>
       </c>
       <c r="C37" s="19" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D37" s="20" t="s">
         <v>25</v>
@@ -4266,13 +4272,13 @@
     </row>
     <row r="38" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="12" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B38" s="13" t="s">
         <v>23</v>
       </c>
       <c r="C38" s="14" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D38" s="15" t="s">
         <v>25</v>
@@ -4292,13 +4298,13 @@
     </row>
     <row r="39" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="17" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B39" s="18" t="s">
         <v>23</v>
       </c>
       <c r="C39" s="19" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D39" s="20" t="s">
         <v>25</v>
@@ -4318,13 +4324,13 @@
     </row>
     <row r="40" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="12" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B40" s="13" t="s">
         <v>23</v>
       </c>
       <c r="C40" s="14" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D40" s="15" t="s">
         <v>25</v>
@@ -4344,13 +4350,13 @@
     </row>
     <row r="41" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="17" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B41" s="18" t="s">
         <v>23</v>
       </c>
       <c r="C41" s="19" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D41" s="20" t="s">
         <v>25</v>
@@ -4370,13 +4376,13 @@
     </row>
     <row r="42" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="12" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B42" s="13" t="s">
         <v>23</v>
       </c>
       <c r="C42" s="14" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D42" s="15" t="s">
         <v>25</v>
@@ -4396,13 +4402,13 @@
     </row>
     <row r="43" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="17" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B43" s="18" t="s">
         <v>23</v>
       </c>
       <c r="C43" s="19" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D43" s="20" t="s">
         <v>25</v>
@@ -4422,13 +4428,13 @@
     </row>
     <row r="44" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="12" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B44" s="13" t="s">
         <v>23</v>
       </c>
       <c r="C44" s="14" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D44" s="15" t="s">
         <v>25</v>
@@ -4448,13 +4454,13 @@
     </row>
     <row r="45" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="17" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B45" s="18" t="s">
         <v>23</v>
       </c>
       <c r="C45" s="19" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D45" s="20" t="s">
         <v>25</v>
@@ -4474,13 +4480,13 @@
     </row>
     <row r="46" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="12" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B46" s="13" t="s">
         <v>23</v>
       </c>
       <c r="C46" s="14" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D46" s="15" t="s">
         <v>25</v>
@@ -4500,13 +4506,13 @@
     </row>
     <row r="47" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="17" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B47" s="18" t="s">
         <v>23</v>
       </c>
       <c r="C47" s="19" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D47" s="20" t="s">
         <v>25</v>
@@ -4526,13 +4532,13 @@
     </row>
     <row r="48" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="12" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B48" s="13" t="s">
         <v>23</v>
       </c>
       <c r="C48" s="14" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D48" s="15" t="s">
         <v>25</v>
@@ -4552,13 +4558,13 @@
     </row>
     <row r="49" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="17" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B49" s="18" t="s">
         <v>23</v>
       </c>
       <c r="C49" s="19" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D49" s="20" t="s">
         <v>25</v>
@@ -4578,13 +4584,13 @@
     </row>
     <row r="50" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="12" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B50" s="13" t="s">
         <v>23</v>
       </c>
       <c r="C50" s="14" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D50" s="15" t="s">
         <v>25</v>
@@ -4604,13 +4610,13 @@
     </row>
     <row r="51" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="17" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B51" s="18" t="s">
         <v>23</v>
       </c>
       <c r="C51" s="19" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D51" s="20" t="s">
         <v>25</v>
@@ -4630,13 +4636,13 @@
     </row>
     <row r="52" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="12" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B52" s="13" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C52" s="14" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D52" s="15" t="s">
         <v>25</v>
@@ -4651,7 +4657,7 @@
         <v>27</v>
       </c>
       <c r="H52" s="15" t="s">
-        <v>129</v>
+        <v>28</v>
       </c>
     </row>
     <row r="53" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
@@ -4659,7 +4665,7 @@
         <v>130</v>
       </c>
       <c r="B53" s="18" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C53" s="19" t="s">
         <v>131</v>
@@ -4677,7 +4683,7 @@
         <v>27</v>
       </c>
       <c r="H53" s="20" t="s">
-        <v>129</v>
+        <v>28</v>
       </c>
     </row>
     <row r="54" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
@@ -4685,7 +4691,7 @@
         <v>132</v>
       </c>
       <c r="B54" s="13" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C54" s="14" t="s">
         <v>133</v>
@@ -4703,7 +4709,7 @@
         <v>27</v>
       </c>
       <c r="H54" s="15" t="s">
-        <v>129</v>
+        <v>28</v>
       </c>
     </row>
     <row r="55" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
@@ -4711,7 +4717,7 @@
         <v>134</v>
       </c>
       <c r="B55" s="18" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C55" s="19" t="s">
         <v>135</v>
@@ -4729,7 +4735,7 @@
         <v>27</v>
       </c>
       <c r="H55" s="20" t="s">
-        <v>129</v>
+        <v>28</v>
       </c>
     </row>
     <row r="56" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
@@ -4737,7 +4743,7 @@
         <v>136</v>
       </c>
       <c r="B56" s="13" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C56" s="14" t="s">
         <v>137</v>
@@ -4755,7 +4761,7 @@
         <v>27</v>
       </c>
       <c r="H56" s="15" t="s">
-        <v>129</v>
+        <v>28</v>
       </c>
     </row>
     <row r="57" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
@@ -4763,7 +4769,7 @@
         <v>138</v>
       </c>
       <c r="B57" s="18" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C57" s="19" t="s">
         <v>139</v>
@@ -4781,7 +4787,7 @@
         <v>27</v>
       </c>
       <c r="H57" s="20" t="s">
-        <v>129</v>
+        <v>28</v>
       </c>
     </row>
     <row r="58" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
@@ -4789,7 +4795,7 @@
         <v>140</v>
       </c>
       <c r="B58" s="13" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C58" s="14" t="s">
         <v>141</v>
@@ -4807,18 +4813,18 @@
         <v>27</v>
       </c>
       <c r="H58" s="15" t="s">
-        <v>129</v>
+        <v>142</v>
       </c>
     </row>
     <row r="59" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="17" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B59" s="18" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C59" s="19" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D59" s="20" t="s">
         <v>25</v>
@@ -4833,18 +4839,18 @@
         <v>27</v>
       </c>
       <c r="H59" s="20" t="s">
-        <v>129</v>
+        <v>145</v>
       </c>
     </row>
     <row r="60" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="12" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B60" s="13" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C60" s="14" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="D60" s="15" t="s">
         <v>25</v>
@@ -4859,18 +4865,18 @@
         <v>27</v>
       </c>
       <c r="H60" s="15" t="s">
-        <v>129</v>
+        <v>28</v>
       </c>
     </row>
     <row r="61" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A61" s="17" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B61" s="18" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C61" s="19" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D61" s="20" t="s">
         <v>25</v>
@@ -4885,18 +4891,18 @@
         <v>27</v>
       </c>
       <c r="H61" s="20" t="s">
-        <v>129</v>
+        <v>28</v>
       </c>
     </row>
     <row r="62" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A62" s="12" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B62" s="13" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C62" s="14" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="D62" s="15" t="s">
         <v>25</v>
@@ -4916,13 +4922,13 @@
     </row>
     <row r="63" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="17" t="s">
+        <v>153</v>
+      </c>
+      <c r="B63" s="18" t="s">
         <v>151</v>
       </c>
-      <c r="B63" s="18" t="s">
-        <v>149</v>
-      </c>
       <c r="C63" s="19" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D63" s="20" t="s">
         <v>25</v>
@@ -4942,13 +4948,13 @@
     </row>
     <row r="64" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A64" s="12" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B64" s="13" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C64" s="14" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D64" s="15" t="s">
         <v>25</v>
@@ -4968,13 +4974,13 @@
     </row>
     <row r="65" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65" s="17" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B65" s="18" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C65" s="19" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D65" s="20" t="s">
         <v>25</v>
@@ -4994,13 +5000,13 @@
     </row>
     <row r="66" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="12" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B66" s="13" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C66" s="14" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D66" s="15" t="s">
         <v>25</v>
@@ -5020,13 +5026,13 @@
     </row>
     <row r="67" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A67" s="17" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B67" s="18" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C67" s="19" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D67" s="20" t="s">
         <v>25</v>
@@ -5046,13 +5052,13 @@
     </row>
     <row r="68" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A68" s="12" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B68" s="13" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C68" s="14" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D68" s="15" t="s">
         <v>25</v>
@@ -5072,13 +5078,13 @@
     </row>
     <row r="69" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A69" s="17" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B69" s="18" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C69" s="19" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D69" s="20" t="s">
         <v>25</v>
@@ -5098,13 +5104,13 @@
     </row>
     <row r="70" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A70" s="12" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B70" s="13" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C70" s="14" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="D70" s="15" t="s">
         <v>25</v>
@@ -5124,13 +5130,13 @@
     </row>
     <row r="71" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A71" s="17" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B71" s="18" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C71" s="19" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="D71" s="20" t="s">
         <v>25</v>
@@ -5150,13 +5156,13 @@
     </row>
     <row r="72" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A72" s="12" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B72" s="13" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C72" s="14" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D72" s="15" t="s">
         <v>25</v>
@@ -5176,13 +5182,13 @@
     </row>
     <row r="73" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A73" s="17" t="s">
+        <v>174</v>
+      </c>
+      <c r="B73" s="18" t="s">
         <v>172</v>
       </c>
-      <c r="B73" s="18" t="s">
-        <v>170</v>
-      </c>
       <c r="C73" s="19" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D73" s="20" t="s">
         <v>25</v>
@@ -5202,13 +5208,13 @@
     </row>
     <row r="74" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A74" s="12" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B74" s="13" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C74" s="14" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D74" s="15" t="s">
         <v>25</v>
@@ -5228,13 +5234,13 @@
     </row>
     <row r="75" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A75" s="17" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B75" s="18" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C75" s="19" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="D75" s="20" t="s">
         <v>25</v>
@@ -5254,13 +5260,13 @@
     </row>
     <row r="76" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A76" s="12" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B76" s="13" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C76" s="14" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="D76" s="15" t="s">
         <v>25</v>
@@ -5280,13 +5286,13 @@
     </row>
     <row r="77" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A77" s="17" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B77" s="18" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C77" s="19" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D77" s="20" t="s">
         <v>25</v>
@@ -5306,13 +5312,13 @@
     </row>
     <row r="78" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A78" s="12" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B78" s="13" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C78" s="14" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="D78" s="15" t="s">
         <v>25</v>
@@ -5332,13 +5338,13 @@
     </row>
     <row r="79" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A79" s="17" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B79" s="18" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C79" s="19" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D79" s="20" t="s">
         <v>25</v>
@@ -5358,13 +5364,13 @@
     </row>
     <row r="80" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A80" s="12" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B80" s="13" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C80" s="14" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D80" s="15" t="s">
         <v>25</v>
@@ -5384,13 +5390,13 @@
     </row>
     <row r="81" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A81" s="17" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B81" s="18" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C81" s="19" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D81" s="20" t="s">
         <v>25</v>
@@ -5410,13 +5416,13 @@
     </row>
     <row r="82" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A82" s="12" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B82" s="13" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C82" s="14" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D82" s="15" t="s">
         <v>25</v>
@@ -5436,13 +5442,13 @@
     </row>
     <row r="83" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A83" s="17" t="s">
+        <v>195</v>
+      </c>
+      <c r="B83" s="18" t="s">
         <v>193</v>
       </c>
-      <c r="B83" s="18" t="s">
-        <v>191</v>
-      </c>
       <c r="C83" s="19" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="D83" s="20" t="s">
         <v>25</v>
@@ -5462,13 +5468,13 @@
     </row>
     <row r="84" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A84" s="12" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B84" s="13" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C84" s="14" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="D84" s="15" t="s">
         <v>25</v>
@@ -5488,13 +5494,13 @@
     </row>
     <row r="85" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A85" s="17" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B85" s="18" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C85" s="19" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D85" s="20" t="s">
         <v>25</v>
@@ -5514,13 +5520,13 @@
     </row>
     <row r="86" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A86" s="12" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B86" s="13" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C86" s="14" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="D86" s="15" t="s">
         <v>25</v>
@@ -5540,13 +5546,13 @@
     </row>
     <row r="87" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A87" s="17" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B87" s="18" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C87" s="19" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D87" s="20" t="s">
         <v>25</v>
@@ -5566,13 +5572,13 @@
     </row>
     <row r="88" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A88" s="12" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B88" s="13" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C88" s="14" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D88" s="15" t="s">
         <v>25</v>
@@ -5592,13 +5598,13 @@
     </row>
     <row r="89" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A89" s="17" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B89" s="18" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C89" s="19" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="D89" s="20" t="s">
         <v>25</v>
@@ -5618,13 +5624,13 @@
     </row>
     <row r="90" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A90" s="12" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B90" s="13" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C90" s="14" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="D90" s="15" t="s">
         <v>25</v>
@@ -5644,13 +5650,13 @@
     </row>
     <row r="91" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A91" s="17" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B91" s="18" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C91" s="19" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="D91" s="20" t="s">
         <v>25</v>
@@ -5670,13 +5676,13 @@
     </row>
     <row r="92" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A92" s="12" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B92" s="13" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C92" s="14" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="D92" s="15" t="s">
         <v>25</v>
@@ -5696,13 +5702,13 @@
     </row>
     <row r="93" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A93" s="17" t="s">
+        <v>216</v>
+      </c>
+      <c r="B93" s="18" t="s">
         <v>214</v>
       </c>
-      <c r="B93" s="18" t="s">
-        <v>212</v>
-      </c>
       <c r="C93" s="19" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="D93" s="20" t="s">
         <v>25</v>
@@ -5722,13 +5728,13 @@
     </row>
     <row r="94" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A94" s="12" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B94" s="13" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C94" s="14" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="D94" s="15" t="s">
         <v>25</v>
@@ -5748,13 +5754,13 @@
     </row>
     <row r="95" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A95" s="17" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B95" s="18" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C95" s="19" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="D95" s="20" t="s">
         <v>25</v>
@@ -5774,13 +5780,13 @@
     </row>
     <row r="96" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A96" s="12" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B96" s="13" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C96" s="14" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="D96" s="15" t="s">
         <v>25</v>
@@ -5800,13 +5806,13 @@
     </row>
     <row r="97" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A97" s="17" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="B97" s="18" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C97" s="19" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="D97" s="20" t="s">
         <v>25</v>
@@ -5826,13 +5832,13 @@
     </row>
     <row r="98" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A98" s="12" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B98" s="13" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C98" s="14" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="D98" s="15" t="s">
         <v>25</v>
@@ -5852,13 +5858,13 @@
     </row>
     <row r="99" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A99" s="17" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B99" s="18" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C99" s="19" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="D99" s="20" t="s">
         <v>25</v>
@@ -5878,13 +5884,13 @@
     </row>
     <row r="100" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A100" s="12" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="B100" s="13" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C100" s="14" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D100" s="15" t="s">
         <v>25</v>
@@ -5904,13 +5910,13 @@
     </row>
     <row r="101" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A101" s="17" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B101" s="18" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C101" s="19" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="D101" s="20" t="s">
         <v>25</v>
@@ -5930,13 +5936,13 @@
     </row>
     <row r="102" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A102" s="12" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B102" s="13" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C102" s="14" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="D102" s="15" t="s">
         <v>25</v>
@@ -5956,13 +5962,13 @@
     </row>
     <row r="103" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A103" s="17" t="s">
+        <v>237</v>
+      </c>
+      <c r="B103" s="18" t="s">
         <v>235</v>
       </c>
-      <c r="B103" s="18" t="s">
-        <v>233</v>
-      </c>
       <c r="C103" s="19" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="D103" s="20" t="s">
         <v>25</v>
@@ -5982,13 +5988,13 @@
     </row>
     <row r="104" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A104" s="12" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B104" s="13" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C104" s="14" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="D104" s="15" t="s">
         <v>25</v>
@@ -6008,13 +6014,13 @@
     </row>
     <row r="105" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A105" s="17" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B105" s="18" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C105" s="19" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="D105" s="20" t="s">
         <v>25</v>
@@ -6034,13 +6040,13 @@
     </row>
     <row r="106" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A106" s="12" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B106" s="13" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C106" s="14" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D106" s="15" t="s">
         <v>25</v>
@@ -6060,13 +6066,13 @@
     </row>
     <row r="107" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A107" s="17" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B107" s="18" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C107" s="19" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D107" s="20" t="s">
         <v>25</v>
@@ -6086,13 +6092,13 @@
     </row>
     <row r="108" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A108" s="12" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B108" s="13" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C108" s="14" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="D108" s="15" t="s">
         <v>25</v>
@@ -6112,13 +6118,13 @@
     </row>
     <row r="109" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A109" s="17" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B109" s="18" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C109" s="19" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="D109" s="20" t="s">
         <v>25</v>
@@ -6138,13 +6144,13 @@
     </row>
     <row r="110" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A110" s="12" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B110" s="13" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C110" s="14" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="D110" s="15" t="s">
         <v>25</v>
@@ -6164,13 +6170,13 @@
     </row>
     <row r="111" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A111" s="17" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B111" s="18" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C111" s="19" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="D111" s="20" t="s">
         <v>25</v>
@@ -6190,13 +6196,13 @@
     </row>
     <row r="112" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A112" s="12" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B112" s="13" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C112" s="14" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="D112" s="15" t="s">
         <v>25</v>
@@ -6216,13 +6222,13 @@
     </row>
     <row r="113" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A113" s="17" t="s">
+        <v>258</v>
+      </c>
+      <c r="B113" s="18" t="s">
         <v>256</v>
       </c>
-      <c r="B113" s="18" t="s">
-        <v>254</v>
-      </c>
       <c r="C113" s="19" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="D113" s="20" t="s">
         <v>25</v>
@@ -6242,13 +6248,13 @@
     </row>
     <row r="114" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A114" s="12" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B114" s="13" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C114" s="14" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D114" s="15" t="s">
         <v>25</v>
@@ -6268,13 +6274,13 @@
     </row>
     <row r="115" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A115" s="17" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B115" s="18" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C115" s="19" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D115" s="20" t="s">
         <v>25</v>
@@ -6294,13 +6300,13 @@
     </row>
     <row r="116" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A116" s="12" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B116" s="13" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C116" s="14" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="D116" s="15" t="s">
         <v>25</v>
@@ -6320,13 +6326,13 @@
     </row>
     <row r="117" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A117" s="17" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B117" s="18" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C117" s="19" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="D117" s="20" t="s">
         <v>25</v>
@@ -6346,13 +6352,13 @@
     </row>
     <row r="118" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A118" s="12" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B118" s="13" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C118" s="14" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D118" s="15" t="s">
         <v>25</v>
@@ -6372,13 +6378,13 @@
     </row>
     <row r="119" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A119" s="17" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B119" s="18" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C119" s="19" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="D119" s="20" t="s">
         <v>25</v>
@@ -6398,13 +6404,13 @@
     </row>
     <row r="120" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A120" s="12" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B120" s="13" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C120" s="14" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="D120" s="15" t="s">
         <v>25</v>
@@ -6424,13 +6430,13 @@
     </row>
     <row r="121" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A121" s="17" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B121" s="18" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C121" s="19" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="D121" s="20" t="s">
         <v>25</v>
@@ -6450,13 +6456,13 @@
     </row>
     <row r="122" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A122" s="12" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B122" s="13" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="C122" s="14" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="D122" s="15" t="s">
         <v>25</v>
@@ -6476,13 +6482,13 @@
     </row>
     <row r="123" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A123" s="17" t="s">
+        <v>279</v>
+      </c>
+      <c r="B123" s="18" t="s">
         <v>277</v>
       </c>
-      <c r="B123" s="18" t="s">
-        <v>275</v>
-      </c>
       <c r="C123" s="19" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="D123" s="20" t="s">
         <v>25</v>
@@ -6502,13 +6508,13 @@
     </row>
     <row r="124" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A124" s="12" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B124" s="13" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="C124" s="14" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="D124" s="15" t="s">
         <v>25</v>
@@ -6528,13 +6534,13 @@
     </row>
     <row r="125" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A125" s="17" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B125" s="18" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="C125" s="19" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="D125" s="20" t="s">
         <v>25</v>
@@ -6554,13 +6560,13 @@
     </row>
     <row r="126" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A126" s="12" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B126" s="13" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="C126" s="14" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="D126" s="15" t="s">
         <v>25</v>
@@ -6580,13 +6586,13 @@
     </row>
     <row r="127" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A127" s="17" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B127" s="18" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="C127" s="19" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="D127" s="20" t="s">
         <v>25</v>
@@ -6606,13 +6612,13 @@
     </row>
     <row r="128" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A128" s="12" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B128" s="13" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="C128" s="14" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="D128" s="15" t="s">
         <v>25</v>
@@ -6632,13 +6638,13 @@
     </row>
     <row r="129" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A129" s="17" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B129" s="18" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="C129" s="19" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="D129" s="20" t="s">
         <v>25</v>
@@ -6658,13 +6664,13 @@
     </row>
     <row r="130" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A130" s="12" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B130" s="13" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="C130" s="14" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="D130" s="15" t="s">
         <v>25</v>
@@ -6684,13 +6690,13 @@
     </row>
     <row r="131" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A131" s="17" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B131" s="18" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="C131" s="19" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="D131" s="20" t="s">
         <v>25</v>
@@ -6710,13 +6716,13 @@
     </row>
     <row r="132" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A132" s="12" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B132" s="13" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C132" s="14" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D132" s="15" t="s">
         <v>25</v>
@@ -6736,13 +6742,13 @@
     </row>
     <row r="133" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A133" s="17" t="s">
+        <v>300</v>
+      </c>
+      <c r="B133" s="18" t="s">
         <v>298</v>
       </c>
-      <c r="B133" s="18" t="s">
-        <v>296</v>
-      </c>
       <c r="C133" s="19" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="D133" s="20" t="s">
         <v>25</v>
@@ -6762,13 +6768,13 @@
     </row>
     <row r="134" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A134" s="12" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B134" s="13" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C134" s="14" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="D134" s="15" t="s">
         <v>25</v>
@@ -6788,13 +6794,13 @@
     </row>
     <row r="135" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A135" s="17" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B135" s="18" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C135" s="19" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="D135" s="20" t="s">
         <v>25</v>
@@ -6814,13 +6820,13 @@
     </row>
     <row r="136" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A136" s="12" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B136" s="13" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C136" s="14" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="D136" s="15" t="s">
         <v>25</v>
@@ -6840,13 +6846,13 @@
     </row>
     <row r="137" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A137" s="17" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B137" s="18" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C137" s="19" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="D137" s="20" t="s">
         <v>25</v>
@@ -6866,13 +6872,13 @@
     </row>
     <row r="138" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A138" s="12" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B138" s="13" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C138" s="14" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="D138" s="15" t="s">
         <v>25</v>
@@ -6892,13 +6898,13 @@
     </row>
     <row r="139" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A139" s="17" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B139" s="18" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C139" s="19" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="D139" s="20" t="s">
         <v>25</v>
@@ -6918,13 +6924,13 @@
     </row>
     <row r="140" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A140" s="12" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B140" s="13" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C140" s="14" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="D140" s="15" t="s">
         <v>25</v>
@@ -6944,13 +6950,13 @@
     </row>
     <row r="141" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A141" s="17" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B141" s="18" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C141" s="19" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="D141" s="20" t="s">
         <v>25</v>
@@ -6970,13 +6976,13 @@
     </row>
     <row r="142" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A142" s="12" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B142" s="13" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="C142" s="14" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="D142" s="15" t="s">
         <v>25</v>
@@ -6996,13 +7002,13 @@
     </row>
     <row r="143" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A143" s="17" t="s">
+        <v>321</v>
+      </c>
+      <c r="B143" s="18" t="s">
         <v>319</v>
       </c>
-      <c r="B143" s="18" t="s">
-        <v>317</v>
-      </c>
       <c r="C143" s="19" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="D143" s="20" t="s">
         <v>25</v>
@@ -7022,13 +7028,13 @@
     </row>
     <row r="144" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A144" s="12" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="B144" s="13" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="C144" s="14" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="D144" s="15" t="s">
         <v>25</v>
@@ -7048,13 +7054,13 @@
     </row>
     <row r="145" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A145" s="17" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B145" s="18" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="C145" s="19" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="D145" s="20" t="s">
         <v>25</v>
@@ -7074,13 +7080,13 @@
     </row>
     <row r="146" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A146" s="12" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B146" s="13" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="C146" s="14" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="D146" s="15" t="s">
         <v>25</v>
@@ -7100,13 +7106,13 @@
     </row>
     <row r="147" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A147" s="17" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="B147" s="18" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="C147" s="19" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="D147" s="20" t="s">
         <v>25</v>
@@ -7126,13 +7132,13 @@
     </row>
     <row r="148" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A148" s="12" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B148" s="13" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="C148" s="14" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D148" s="15" t="s">
         <v>25</v>
@@ -7152,13 +7158,13 @@
     </row>
     <row r="149" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A149" s="17" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="B149" s="18" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="C149" s="19" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="D149" s="20" t="s">
         <v>25</v>
@@ -7178,13 +7184,13 @@
     </row>
     <row r="150" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A150" s="12" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="B150" s="13" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="C150" s="14" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="D150" s="15" t="s">
         <v>25</v>
@@ -7204,13 +7210,13 @@
     </row>
     <row r="151" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A151" s="17" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B151" s="18" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="C151" s="19" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="D151" s="20" t="s">
         <v>25</v>
@@ -7230,13 +7236,13 @@
     </row>
     <row r="152" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A152" s="12" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B152" s="13" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="C152" s="14" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="D152" s="15" t="s">
         <v>25</v>
@@ -7256,13 +7262,13 @@
     </row>
     <row r="153" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A153" s="17" t="s">
+        <v>342</v>
+      </c>
+      <c r="B153" s="18" t="s">
         <v>340</v>
       </c>
-      <c r="B153" s="18" t="s">
-        <v>338</v>
-      </c>
       <c r="C153" s="19" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="D153" s="20" t="s">
         <v>25</v>
@@ -7282,13 +7288,13 @@
     </row>
     <row r="154" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A154" s="12" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B154" s="13" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="C154" s="14" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="D154" s="15" t="s">
         <v>25</v>
@@ -7308,13 +7314,13 @@
     </row>
     <row r="155" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A155" s="17" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B155" s="18" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="C155" s="19" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="D155" s="20" t="s">
         <v>25</v>
@@ -7334,13 +7340,13 @@
     </row>
     <row r="156" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A156" s="12" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B156" s="13" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="C156" s="14" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="D156" s="15" t="s">
         <v>25</v>
@@ -7360,13 +7366,13 @@
     </row>
     <row r="157" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A157" s="17" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="B157" s="18" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="C157" s="19" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="D157" s="20" t="s">
         <v>25</v>
@@ -7386,13 +7392,13 @@
     </row>
     <row r="158" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A158" s="12" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="B158" s="13" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="C158" s="14" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="D158" s="15" t="s">
         <v>25</v>
@@ -7412,13 +7418,13 @@
     </row>
     <row r="159" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A159" s="17" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="B159" s="18" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="C159" s="19" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="D159" s="20" t="s">
         <v>25</v>
@@ -7438,13 +7444,13 @@
     </row>
     <row r="160" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A160" s="12" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="B160" s="13" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="C160" s="14" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="D160" s="15" t="s">
         <v>25</v>
@@ -7464,13 +7470,13 @@
     </row>
     <row r="161" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A161" s="17" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="B161" s="18" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="C161" s="19" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="D161" s="20" t="s">
         <v>25</v>
@@ -7490,13 +7496,13 @@
     </row>
     <row r="162" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A162" s="12" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="B162" s="13" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C162" s="14" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="D162" s="15" t="s">
         <v>25</v>
@@ -7516,13 +7522,13 @@
     </row>
     <row r="163" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A163" s="17" t="s">
+        <v>363</v>
+      </c>
+      <c r="B163" s="18" t="s">
         <v>361</v>
       </c>
-      <c r="B163" s="18" t="s">
-        <v>359</v>
-      </c>
       <c r="C163" s="19" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="D163" s="20" t="s">
         <v>25</v>
@@ -7542,13 +7548,13 @@
     </row>
     <row r="164" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A164" s="12" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B164" s="13" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C164" s="14" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="D164" s="15" t="s">
         <v>25</v>
@@ -7568,13 +7574,13 @@
     </row>
     <row r="165" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A165" s="17" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="B165" s="18" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C165" s="19" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="D165" s="20" t="s">
         <v>25</v>
@@ -7594,13 +7600,13 @@
     </row>
     <row r="166" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A166" s="12" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="B166" s="13" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C166" s="14" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="D166" s="15" t="s">
         <v>25</v>
@@ -7620,13 +7626,13 @@
     </row>
     <row r="167" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A167" s="17" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B167" s="18" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C167" s="19" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="D167" s="20" t="s">
         <v>25</v>
@@ -7646,13 +7652,13 @@
     </row>
     <row r="168" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A168" s="12" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="B168" s="13" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C168" s="14" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="D168" s="15" t="s">
         <v>25</v>
@@ -7672,13 +7678,13 @@
     </row>
     <row r="169" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A169" s="17" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="B169" s="18" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C169" s="19" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="D169" s="20" t="s">
         <v>25</v>
@@ -7698,13 +7704,13 @@
     </row>
     <row r="170" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A170" s="12" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="B170" s="13" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C170" s="14" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="D170" s="15" t="s">
         <v>25</v>
@@ -7724,13 +7730,13 @@
     </row>
     <row r="171" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A171" s="17" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="B171" s="18" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C171" s="19" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="D171" s="20" t="s">
         <v>25</v>
@@ -7750,13 +7756,13 @@
     </row>
     <row r="172" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A172" s="12" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B172" s="13" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="C172" s="14" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="D172" s="15" t="s">
         <v>25</v>
@@ -7776,13 +7782,13 @@
     </row>
     <row r="173" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A173" s="17" t="s">
+        <v>384</v>
+      </c>
+      <c r="B173" s="18" t="s">
         <v>382</v>
       </c>
-      <c r="B173" s="18" t="s">
-        <v>380</v>
-      </c>
       <c r="C173" s="19" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="D173" s="20" t="s">
         <v>25</v>
@@ -7802,13 +7808,13 @@
     </row>
     <row r="174" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A174" s="12" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="B174" s="13" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="C174" s="14" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="D174" s="15" t="s">
         <v>25</v>
@@ -7828,13 +7834,13 @@
     </row>
     <row r="175" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A175" s="17" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B175" s="18" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="C175" s="19" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="D175" s="20" t="s">
         <v>25</v>
@@ -7854,13 +7860,13 @@
     </row>
     <row r="176" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A176" s="12" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="B176" s="13" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="C176" s="14" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="D176" s="15" t="s">
         <v>25</v>
@@ -7880,13 +7886,13 @@
     </row>
     <row r="177" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A177" s="17" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="B177" s="18" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="C177" s="19" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="D177" s="20" t="s">
         <v>25</v>
@@ -7906,13 +7912,13 @@
     </row>
     <row r="178" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A178" s="12" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="B178" s="13" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="C178" s="14" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="D178" s="15" t="s">
         <v>25</v>
@@ -7932,13 +7938,13 @@
     </row>
     <row r="179" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A179" s="17" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="B179" s="18" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="C179" s="19" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="D179" s="20" t="s">
         <v>25</v>
@@ -7958,13 +7964,13 @@
     </row>
     <row r="180" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A180" s="12" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B180" s="13" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="C180" s="14" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="D180" s="15" t="s">
         <v>25</v>
@@ -7984,13 +7990,13 @@
     </row>
     <row r="181" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A181" s="17" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B181" s="18" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="C181" s="19" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="D181" s="20" t="s">
         <v>25</v>
@@ -8010,13 +8016,13 @@
     </row>
     <row r="182" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A182" s="12" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B182" s="13" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C182" s="14" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="D182" s="15" t="s">
         <v>25</v>
@@ -8036,13 +8042,13 @@
     </row>
     <row r="183" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A183" s="17" t="s">
+        <v>405</v>
+      </c>
+      <c r="B183" s="18" t="s">
         <v>403</v>
       </c>
-      <c r="B183" s="18" t="s">
-        <v>401</v>
-      </c>
       <c r="C183" s="19" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="D183" s="20" t="s">
         <v>25</v>
@@ -8062,13 +8068,13 @@
     </row>
     <row r="184" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A184" s="12" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="B184" s="13" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C184" s="14" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="D184" s="15" t="s">
         <v>25</v>
@@ -8088,13 +8094,13 @@
     </row>
     <row r="185" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A185" s="17" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="B185" s="18" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C185" s="19" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="D185" s="20" t="s">
         <v>25</v>
@@ -8114,13 +8120,13 @@
     </row>
     <row r="186" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A186" s="12" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="B186" s="13" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C186" s="14" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="D186" s="15" t="s">
         <v>25</v>
@@ -8140,13 +8146,13 @@
     </row>
     <row r="187" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A187" s="17" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="B187" s="18" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C187" s="19" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="D187" s="20" t="s">
         <v>25</v>
@@ -8166,13 +8172,13 @@
     </row>
     <row r="188" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A188" s="12" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="B188" s="13" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C188" s="14" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="D188" s="15" t="s">
         <v>25</v>
@@ -8192,13 +8198,13 @@
     </row>
     <row r="189" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A189" s="17" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="B189" s="18" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C189" s="19" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="D189" s="20" t="s">
         <v>25</v>
@@ -8218,13 +8224,13 @@
     </row>
     <row r="190" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A190" s="12" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="B190" s="13" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C190" s="14" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="D190" s="15" t="s">
         <v>25</v>
@@ -8244,13 +8250,13 @@
     </row>
     <row r="191" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A191" s="17" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="B191" s="18" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="C191" s="19" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="D191" s="20" t="s">
         <v>25</v>
@@ -8270,13 +8276,13 @@
     </row>
     <row r="192" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A192" s="12" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="B192" s="13" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="C192" s="14" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="D192" s="15" t="s">
         <v>25</v>
@@ -8296,13 +8302,13 @@
     </row>
     <row r="193" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A193" s="17" t="s">
+        <v>426</v>
+      </c>
+      <c r="B193" s="18" t="s">
         <v>424</v>
       </c>
-      <c r="B193" s="18" t="s">
-        <v>422</v>
-      </c>
       <c r="C193" s="19" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="D193" s="20" t="s">
         <v>25</v>
@@ -8322,13 +8328,13 @@
     </row>
     <row r="194" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A194" s="12" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="B194" s="13" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="C194" s="14" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="D194" s="15" t="s">
         <v>25</v>
@@ -8348,13 +8354,13 @@
     </row>
     <row r="195" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A195" s="17" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="B195" s="18" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="C195" s="19" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="D195" s="20" t="s">
         <v>25</v>
@@ -8374,13 +8380,13 @@
     </row>
     <row r="196" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A196" s="12" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="B196" s="13" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="C196" s="14" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="D196" s="15" t="s">
         <v>25</v>
@@ -8400,13 +8406,13 @@
     </row>
     <row r="197" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A197" s="17" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B197" s="18" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="C197" s="19" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="D197" s="20" t="s">
         <v>25</v>
@@ -8426,13 +8432,13 @@
     </row>
     <row r="198" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A198" s="12" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="B198" s="13" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="C198" s="14" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="D198" s="15" t="s">
         <v>25</v>
@@ -8452,13 +8458,13 @@
     </row>
     <row r="199" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A199" s="17" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="B199" s="18" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="C199" s="19" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="D199" s="20" t="s">
         <v>25</v>
@@ -8478,13 +8484,13 @@
     </row>
     <row r="200" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A200" s="12" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="B200" s="13" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="C200" s="14" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="D200" s="15" t="s">
         <v>25</v>
@@ -8504,13 +8510,13 @@
     </row>
     <row r="201" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A201" s="17" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="B201" s="18" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="C201" s="19" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="D201" s="20" t="s">
         <v>25</v>
@@ -8530,13 +8536,13 @@
     </row>
     <row r="202" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A202" s="12" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="B202" s="13" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C202" s="14" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="D202" s="15" t="s">
         <v>25</v>
@@ -8556,13 +8562,13 @@
     </row>
     <row r="203" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A203" s="17" t="s">
+        <v>447</v>
+      </c>
+      <c r="B203" s="18" t="s">
         <v>445</v>
       </c>
-      <c r="B203" s="18" t="s">
-        <v>443</v>
-      </c>
       <c r="C203" s="19" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="D203" s="20" t="s">
         <v>25</v>
@@ -8582,13 +8588,13 @@
     </row>
     <row r="204" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A204" s="12" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="B204" s="13" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C204" s="14" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="D204" s="15" t="s">
         <v>25</v>
@@ -8608,13 +8614,13 @@
     </row>
     <row r="205" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A205" s="17" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="B205" s="18" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C205" s="19" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="D205" s="20" t="s">
         <v>25</v>
@@ -8634,13 +8640,13 @@
     </row>
     <row r="206" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A206" s="12" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="B206" s="13" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C206" s="14" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="D206" s="15" t="s">
         <v>25</v>
@@ -8660,13 +8666,13 @@
     </row>
     <row r="207" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A207" s="17" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="B207" s="18" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C207" s="19" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="D207" s="20" t="s">
         <v>25</v>
@@ -8686,13 +8692,13 @@
     </row>
     <row r="208" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A208" s="12" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="B208" s="13" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C208" s="14" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="D208" s="15" t="s">
         <v>25</v>
@@ -8712,13 +8718,13 @@
     </row>
     <row r="209" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A209" s="17" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="B209" s="18" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C209" s="19" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="D209" s="20" t="s">
         <v>25</v>
@@ -8738,13 +8744,13 @@
     </row>
     <row r="210" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A210" s="12" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="B210" s="13" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C210" s="14" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="D210" s="15" t="s">
         <v>25</v>
@@ -8764,13 +8770,13 @@
     </row>
     <row r="211" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A211" s="17" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="B211" s="18" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C211" s="19" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="D211" s="20" t="s">
         <v>25</v>
@@ -8790,13 +8796,13 @@
     </row>
     <row r="212" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A212" s="12" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="B212" s="13" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="C212" s="14" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="D212" s="15" t="s">
         <v>25</v>
@@ -8816,13 +8822,13 @@
     </row>
     <row r="213" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A213" s="17" t="s">
+        <v>468</v>
+      </c>
+      <c r="B213" s="18" t="s">
         <v>466</v>
       </c>
-      <c r="B213" s="18" t="s">
-        <v>464</v>
-      </c>
       <c r="C213" s="19" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="D213" s="20" t="s">
         <v>25</v>
@@ -8842,13 +8848,13 @@
     </row>
     <row r="214" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A214" s="12" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="B214" s="13" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="C214" s="14" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="D214" s="15" t="s">
         <v>25</v>
@@ -8868,13 +8874,13 @@
     </row>
     <row r="215" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A215" s="17" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="B215" s="18" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="C215" s="19" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="D215" s="20" t="s">
         <v>25</v>
@@ -8894,13 +8900,13 @@
     </row>
     <row r="216" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A216" s="12" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="B216" s="13" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="C216" s="14" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="D216" s="15" t="s">
         <v>25</v>
@@ -8920,13 +8926,13 @@
     </row>
     <row r="217" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A217" s="17" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="B217" s="18" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="C217" s="19" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="D217" s="20" t="s">
         <v>25</v>
@@ -8946,13 +8952,13 @@
     </row>
     <row r="218" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A218" s="12" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="B218" s="13" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="C218" s="14" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="D218" s="15" t="s">
         <v>25</v>
@@ -8972,13 +8978,13 @@
     </row>
     <row r="219" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A219" s="17" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="B219" s="18" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="C219" s="19" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="D219" s="20" t="s">
         <v>25</v>
@@ -8998,13 +9004,13 @@
     </row>
     <row r="220" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A220" s="12" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="B220" s="13" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="C220" s="14" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="D220" s="15" t="s">
         <v>25</v>
@@ -9024,13 +9030,13 @@
     </row>
     <row r="221" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A221" s="17" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="B221" s="18" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="C221" s="19" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="D221" s="20" t="s">
         <v>25</v>
@@ -9050,13 +9056,13 @@
     </row>
     <row r="222" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A222" s="12" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="B222" s="13" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="C222" s="14" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="D222" s="15" t="s">
         <v>25</v>
@@ -9076,13 +9082,13 @@
     </row>
     <row r="223" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A223" s="17" t="s">
+        <v>489</v>
+      </c>
+      <c r="B223" s="18" t="s">
         <v>487</v>
       </c>
-      <c r="B223" s="18" t="s">
-        <v>485</v>
-      </c>
       <c r="C223" s="19" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="D223" s="20" t="s">
         <v>25</v>
@@ -9102,13 +9108,13 @@
     </row>
     <row r="224" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A224" s="12" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="B224" s="13" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="C224" s="14" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="D224" s="15" t="s">
         <v>25</v>
@@ -9128,13 +9134,13 @@
     </row>
     <row r="225" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A225" s="17" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="B225" s="18" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="C225" s="19" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="D225" s="20" t="s">
         <v>25</v>
@@ -9154,13 +9160,13 @@
     </row>
     <row r="226" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A226" s="12" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="B226" s="13" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="C226" s="14" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="D226" s="15" t="s">
         <v>25</v>
@@ -9180,13 +9186,13 @@
     </row>
     <row r="227" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A227" s="17" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="B227" s="18" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="C227" s="19" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="D227" s="20" t="s">
         <v>25</v>
@@ -9206,13 +9212,13 @@
     </row>
     <row r="228" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A228" s="12" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="B228" s="13" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="C228" s="14" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="D228" s="15" t="s">
         <v>25</v>
@@ -9232,13 +9238,13 @@
     </row>
     <row r="229" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A229" s="17" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="B229" s="18" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="C229" s="19" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="D229" s="20" t="s">
         <v>25</v>
@@ -9258,13 +9264,13 @@
     </row>
     <row r="230" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A230" s="12" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="B230" s="13" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="C230" s="14" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="D230" s="15" t="s">
         <v>25</v>
@@ -9284,13 +9290,13 @@
     </row>
     <row r="231" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A231" s="17" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="B231" s="18" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="C231" s="19" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="D231" s="20" t="s">
         <v>25</v>
@@ -9310,13 +9316,13 @@
     </row>
     <row r="232" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A232" s="12" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="B232" s="13" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="C232" s="14" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="D232" s="15" t="s">
         <v>25</v>
@@ -9336,13 +9342,13 @@
     </row>
     <row r="233" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A233" s="17" t="s">
+        <v>510</v>
+      </c>
+      <c r="B233" s="18" t="s">
         <v>508</v>
       </c>
-      <c r="B233" s="18" t="s">
-        <v>506</v>
-      </c>
       <c r="C233" s="19" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="D233" s="20" t="s">
         <v>25</v>
@@ -9362,13 +9368,13 @@
     </row>
     <row r="234" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A234" s="12" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="B234" s="13" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="C234" s="14" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="D234" s="15" t="s">
         <v>25</v>
@@ -9388,13 +9394,13 @@
     </row>
     <row r="235" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A235" s="17" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="B235" s="18" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="C235" s="19" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="D235" s="20" t="s">
         <v>25</v>
@@ -9414,13 +9420,13 @@
     </row>
     <row r="236" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A236" s="12" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="B236" s="13" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="C236" s="14" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="D236" s="15" t="s">
         <v>25</v>
@@ -9440,13 +9446,13 @@
     </row>
     <row r="237" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A237" s="17" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="B237" s="18" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="C237" s="19" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="D237" s="20" t="s">
         <v>25</v>
@@ -9466,13 +9472,13 @@
     </row>
     <row r="238" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A238" s="12" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="B238" s="13" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="C238" s="14" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="D238" s="15" t="s">
         <v>25</v>
@@ -9492,13 +9498,13 @@
     </row>
     <row r="239" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A239" s="17" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="B239" s="18" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="C239" s="19" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="D239" s="20" t="s">
         <v>25</v>
@@ -9518,13 +9524,13 @@
     </row>
     <row r="240" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A240" s="12" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="B240" s="13" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="C240" s="14" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="D240" s="15" t="s">
         <v>25</v>
@@ -9544,13 +9550,13 @@
     </row>
     <row r="241" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A241" s="17" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="B241" s="18" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="C241" s="19" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="D241" s="20" t="s">
         <v>25</v>
@@ -9570,13 +9576,13 @@
     </row>
     <row r="242" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A242" s="12" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="B242" s="13" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="C242" s="14" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="D242" s="15" t="s">
         <v>25</v>
@@ -9596,13 +9602,13 @@
     </row>
     <row r="243" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A243" s="17" t="s">
+        <v>531</v>
+      </c>
+      <c r="B243" s="18" t="s">
         <v>529</v>
       </c>
-      <c r="B243" s="18" t="s">
-        <v>527</v>
-      </c>
       <c r="C243" s="19" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="D243" s="20" t="s">
         <v>25</v>
@@ -9622,13 +9628,13 @@
     </row>
     <row r="244" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A244" s="12" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="B244" s="13" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="C244" s="14" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="D244" s="15" t="s">
         <v>25</v>
@@ -9648,13 +9654,13 @@
     </row>
     <row r="245" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A245" s="17" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="B245" s="18" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="C245" s="19" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="D245" s="20" t="s">
         <v>25</v>
@@ -9674,13 +9680,13 @@
     </row>
     <row r="246" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A246" s="12" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="B246" s="13" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="C246" s="14" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="D246" s="15" t="s">
         <v>25</v>
@@ -9700,13 +9706,13 @@
     </row>
     <row r="247" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A247" s="17" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="B247" s="18" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="C247" s="19" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="D247" s="20" t="s">
         <v>25</v>
@@ -9726,13 +9732,13 @@
     </row>
     <row r="248" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A248" s="12" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="B248" s="13" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="C248" s="14" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="D248" s="15" t="s">
         <v>25</v>
@@ -9752,13 +9758,13 @@
     </row>
     <row r="249" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A249" s="17" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="B249" s="18" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="C249" s="19" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="D249" s="20" t="s">
         <v>25</v>
@@ -9778,13 +9784,13 @@
     </row>
     <row r="250" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A250" s="12" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="B250" s="13" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="C250" s="14" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="D250" s="15" t="s">
         <v>25</v>
@@ -9804,13 +9810,13 @@
     </row>
     <row r="251" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A251" s="17" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="B251" s="18" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="C251" s="19" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="D251" s="20" t="s">
         <v>25</v>
@@ -9830,13 +9836,13 @@
     </row>
     <row r="252" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A252" s="12" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="B252" s="13" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="C252" s="14" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="D252" s="15" t="s">
         <v>25</v>
@@ -9856,13 +9862,13 @@
     </row>
     <row r="253" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A253" s="17" t="s">
+        <v>552</v>
+      </c>
+      <c r="B253" s="18" t="s">
         <v>550</v>
       </c>
-      <c r="B253" s="18" t="s">
-        <v>548</v>
-      </c>
       <c r="C253" s="19" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="D253" s="20" t="s">
         <v>25</v>
@@ -9882,13 +9888,13 @@
     </row>
     <row r="254" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A254" s="12" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="B254" s="13" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="C254" s="14" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="D254" s="15" t="s">
         <v>25</v>
@@ -9908,13 +9914,13 @@
     </row>
     <row r="255" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A255" s="17" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="B255" s="18" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="C255" s="19" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="D255" s="20" t="s">
         <v>25</v>
@@ -9934,13 +9940,13 @@
     </row>
     <row r="256" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A256" s="12" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="B256" s="13" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="C256" s="14" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="D256" s="15" t="s">
         <v>25</v>
@@ -9960,13 +9966,13 @@
     </row>
     <row r="257" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A257" s="17" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="B257" s="18" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="C257" s="19" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="D257" s="20" t="s">
         <v>25</v>
@@ -9986,13 +9992,13 @@
     </row>
     <row r="258" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A258" s="12" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="B258" s="13" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="C258" s="14" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="D258" s="15" t="s">
         <v>25</v>
@@ -10012,13 +10018,13 @@
     </row>
     <row r="259" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A259" s="17" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="B259" s="18" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="C259" s="19" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="D259" s="20" t="s">
         <v>25</v>
@@ -10038,13 +10044,13 @@
     </row>
     <row r="260" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A260" s="12" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="B260" s="13" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="C260" s="14" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="D260" s="15" t="s">
         <v>25</v>
@@ -10064,13 +10070,13 @@
     </row>
     <row r="261" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A261" s="17" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="B261" s="18" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="C261" s="19" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="D261" s="20" t="s">
         <v>25</v>
@@ -10090,13 +10096,13 @@
     </row>
     <row r="262" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A262" s="12" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="B262" s="13" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="C262" s="14" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="D262" s="15" t="s">
         <v>25</v>
@@ -10116,13 +10122,13 @@
     </row>
     <row r="263" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A263" s="17" t="s">
+        <v>573</v>
+      </c>
+      <c r="B263" s="18" t="s">
         <v>571</v>
       </c>
-      <c r="B263" s="18" t="s">
-        <v>569</v>
-      </c>
       <c r="C263" s="19" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="D263" s="20" t="s">
         <v>25</v>
@@ -10142,13 +10148,13 @@
     </row>
     <row r="264" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A264" s="12" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="B264" s="13" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="C264" s="14" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="D264" s="15" t="s">
         <v>25</v>
@@ -10168,13 +10174,13 @@
     </row>
     <row r="265" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A265" s="17" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="B265" s="18" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="C265" s="19" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="D265" s="20" t="s">
         <v>25</v>
@@ -10194,13 +10200,13 @@
     </row>
     <row r="266" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A266" s="12" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="B266" s="13" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="C266" s="14" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="D266" s="15" t="s">
         <v>25</v>
@@ -10220,13 +10226,13 @@
     </row>
     <row r="267" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A267" s="17" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="B267" s="18" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="C267" s="19" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="D267" s="20" t="s">
         <v>25</v>
@@ -10246,13 +10252,13 @@
     </row>
     <row r="268" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A268" s="12" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="B268" s="13" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="C268" s="14" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="D268" s="15" t="s">
         <v>25</v>
@@ -10272,13 +10278,13 @@
     </row>
     <row r="269" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A269" s="17" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="B269" s="18" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="C269" s="19" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="D269" s="20" t="s">
         <v>25</v>
@@ -10298,13 +10304,13 @@
     </row>
     <row r="270" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A270" s="12" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="B270" s="13" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="C270" s="14" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="D270" s="15" t="s">
         <v>25</v>
@@ -10324,13 +10330,13 @@
     </row>
     <row r="271" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A271" s="17" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="B271" s="18" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="C271" s="19" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="D271" s="20" t="s">
         <v>25</v>
@@ -10350,13 +10356,13 @@
     </row>
     <row r="272" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A272" s="12" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="B272" s="13" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="C272" s="14" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="D272" s="15" t="s">
         <v>25</v>
@@ -10376,13 +10382,13 @@
     </row>
     <row r="273" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A273" s="17" t="s">
+        <v>594</v>
+      </c>
+      <c r="B273" s="18" t="s">
         <v>592</v>
       </c>
-      <c r="B273" s="18" t="s">
-        <v>590</v>
-      </c>
       <c r="C273" s="19" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="D273" s="20" t="s">
         <v>25</v>
@@ -10402,13 +10408,13 @@
     </row>
     <row r="274" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A274" s="12" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="B274" s="13" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="C274" s="14" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="D274" s="15" t="s">
         <v>25</v>
@@ -10428,13 +10434,13 @@
     </row>
     <row r="275" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A275" s="17" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="B275" s="18" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="C275" s="19" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="D275" s="20" t="s">
         <v>25</v>
@@ -10454,13 +10460,13 @@
     </row>
     <row r="276" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A276" s="12" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="B276" s="13" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="C276" s="14" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="D276" s="15" t="s">
         <v>25</v>
@@ -10480,13 +10486,13 @@
     </row>
     <row r="277" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A277" s="17" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="B277" s="18" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="C277" s="19" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="D277" s="20" t="s">
         <v>25</v>
@@ -10506,13 +10512,13 @@
     </row>
     <row r="278" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A278" s="12" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="B278" s="13" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="C278" s="14" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="D278" s="15" t="s">
         <v>25</v>
@@ -10532,13 +10538,13 @@
     </row>
     <row r="279" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A279" s="17" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="B279" s="18" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="C279" s="19" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="D279" s="20" t="s">
         <v>25</v>
@@ -10558,13 +10564,13 @@
     </row>
     <row r="280" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A280" s="12" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="B280" s="13" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="C280" s="14" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="D280" s="15" t="s">
         <v>25</v>
@@ -10584,13 +10590,13 @@
     </row>
     <row r="281" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A281" s="17" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="B281" s="18" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="C281" s="19" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="D281" s="20" t="s">
         <v>25</v>
@@ -10610,13 +10616,13 @@
     </row>
     <row r="282" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A282" s="12" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="B282" s="13" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="C282" s="14" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="D282" s="15" t="s">
         <v>25</v>
@@ -10636,13 +10642,13 @@
     </row>
     <row r="283" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A283" s="17" t="s">
+        <v>615</v>
+      </c>
+      <c r="B283" s="18" t="s">
         <v>613</v>
       </c>
-      <c r="B283" s="18" t="s">
-        <v>611</v>
-      </c>
       <c r="C283" s="19" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="D283" s="20" t="s">
         <v>25</v>
@@ -10662,13 +10668,13 @@
     </row>
     <row r="284" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A284" s="12" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="B284" s="13" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="C284" s="14" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="D284" s="15" t="s">
         <v>25</v>
@@ -10688,13 +10694,13 @@
     </row>
     <row r="285" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A285" s="17" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="B285" s="18" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="C285" s="19" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="D285" s="20" t="s">
         <v>25</v>
@@ -10714,13 +10720,13 @@
     </row>
     <row r="286" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A286" s="12" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="B286" s="13" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="C286" s="14" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="D286" s="15" t="s">
         <v>25</v>
@@ -10740,13 +10746,13 @@
     </row>
     <row r="287" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A287" s="17" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="B287" s="18" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="C287" s="19" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="D287" s="20" t="s">
         <v>25</v>
@@ -10766,13 +10772,13 @@
     </row>
     <row r="288" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A288" s="12" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="B288" s="13" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="C288" s="14" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="D288" s="15" t="s">
         <v>25</v>
@@ -10792,13 +10798,13 @@
     </row>
     <row r="289" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A289" s="17" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="B289" s="18" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="C289" s="19" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="D289" s="20" t="s">
         <v>25</v>
@@ -10818,13 +10824,13 @@
     </row>
     <row r="290" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A290" s="12" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="B290" s="13" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="C290" s="14" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="D290" s="15" t="s">
         <v>25</v>
@@ -10844,13 +10850,13 @@
     </row>
     <row r="291" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A291" s="17" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="B291" s="18" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="C291" s="19" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="D291" s="20" t="s">
         <v>25</v>
@@ -10870,13 +10876,13 @@
     </row>
     <row r="292" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A292" s="12" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="B292" s="13" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="C292" s="14" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="D292" s="15" t="s">
         <v>25</v>
@@ -10896,13 +10902,13 @@
     </row>
     <row r="293" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A293" s="17" t="s">
+        <v>636</v>
+      </c>
+      <c r="B293" s="18" t="s">
         <v>634</v>
       </c>
-      <c r="B293" s="18" t="s">
-        <v>632</v>
-      </c>
       <c r="C293" s="19" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="D293" s="20" t="s">
         <v>25</v>
@@ -10922,13 +10928,13 @@
     </row>
     <row r="294" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A294" s="12" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="B294" s="13" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="C294" s="14" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="D294" s="15" t="s">
         <v>25</v>
@@ -10948,13 +10954,13 @@
     </row>
     <row r="295" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A295" s="17" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="B295" s="18" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="C295" s="19" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="D295" s="20" t="s">
         <v>25</v>
@@ -10974,13 +10980,13 @@
     </row>
     <row r="296" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A296" s="12" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="B296" s="13" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="C296" s="14" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="D296" s="15" t="s">
         <v>25</v>
@@ -11000,13 +11006,13 @@
     </row>
     <row r="297" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A297" s="17" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="B297" s="18" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="C297" s="19" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="D297" s="20" t="s">
         <v>25</v>
@@ -11026,13 +11032,13 @@
     </row>
     <row r="298" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A298" s="12" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="B298" s="13" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="C298" s="14" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="D298" s="15" t="s">
         <v>25</v>
@@ -11052,13 +11058,13 @@
     </row>
     <row r="299" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A299" s="17" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="B299" s="18" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="C299" s="19" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="D299" s="20" t="s">
         <v>25</v>
@@ -11078,13 +11084,13 @@
     </row>
     <row r="300" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A300" s="12" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="B300" s="13" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="C300" s="14" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="D300" s="15" t="s">
         <v>25</v>
@@ -11104,13 +11110,13 @@
     </row>
     <row r="301" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A301" s="17" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="B301" s="18" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="C301" s="19" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="D301" s="20" t="s">
         <v>25</v>
@@ -11151,33 +11157,33 @@
         <v>16</v>
       </c>
       <c r="B1" s="21" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="C1" s="21" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="D1" s="21" t="s">
         <v>17</v>
       </c>
       <c r="E1" s="21" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:5" s="22" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="22" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="B2" s="22" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="C2" s="22" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="D2" s="22" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="E2" s="22" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
     </row>
   </sheetData>
@@ -11200,19 +11206,19 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="23" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="B1" s="23" t="s">
         <v>16</v>
       </c>
       <c r="C1" s="23" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="D1" s="23" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="E1" s="23" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11220,16 +11226,16 @@
         <v>27</v>
       </c>
       <c r="B2" s="24" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="C2" s="24" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="D2" s="25" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="E2" s="24" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11237,16 +11243,16 @@
         <v>27</v>
       </c>
       <c r="B3" s="26" t="s">
+        <v>670</v>
+      </c>
+      <c r="C3" s="26" t="s">
+        <v>671</v>
+      </c>
+      <c r="D3" s="27" t="s">
         <v>668</v>
       </c>
-      <c r="C3" s="26" t="s">
+      <c r="E3" s="26" t="s">
         <v>669</v>
-      </c>
-      <c r="D3" s="27" t="s">
-        <v>666</v>
-      </c>
-      <c r="E3" s="26" t="s">
-        <v>667</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11254,16 +11260,16 @@
         <v>27</v>
       </c>
       <c r="B4" s="24" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="C4" s="24" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="D4" s="25" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="E4" s="24" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11271,16 +11277,16 @@
         <v>27</v>
       </c>
       <c r="B5" s="26" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="C5" s="26" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="D5" s="27" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="E5" s="26" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11288,16 +11294,16 @@
         <v>27</v>
       </c>
       <c r="B6" s="24" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="C6" s="24" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="D6" s="25" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="E6" s="24" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11305,16 +11311,16 @@
         <v>27</v>
       </c>
       <c r="B7" s="26" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="C7" s="26" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="D7" s="27" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="E7" s="26" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11322,16 +11328,16 @@
         <v>27</v>
       </c>
       <c r="B8" s="24" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="C8" s="24" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="D8" s="25" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="E8" s="24" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11339,16 +11345,16 @@
         <v>27</v>
       </c>
       <c r="B9" s="26" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="C9" s="26" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="D9" s="27" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="E9" s="26" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11356,16 +11362,16 @@
         <v>27</v>
       </c>
       <c r="B10" s="24" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="C10" s="24" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="D10" s="25" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="E10" s="24" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11373,16 +11379,16 @@
         <v>27</v>
       </c>
       <c r="B11" s="26" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="C11" s="26" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="D11" s="27" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="E11" s="26" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11390,16 +11396,16 @@
         <v>27</v>
       </c>
       <c r="B12" s="24" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="C12" s="24" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="D12" s="25" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="E12" s="24" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11407,16 +11413,16 @@
         <v>27</v>
       </c>
       <c r="B13" s="26" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="C13" s="26" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="D13" s="27" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="E13" s="26" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11424,16 +11430,16 @@
         <v>27</v>
       </c>
       <c r="B14" s="24" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="C14" s="24" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="D14" s="25" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="E14" s="24" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11441,16 +11447,16 @@
         <v>27</v>
       </c>
       <c r="B15" s="26" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="C15" s="26" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="D15" s="27" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="E15" s="26" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11458,16 +11464,16 @@
         <v>27</v>
       </c>
       <c r="B16" s="24" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="C16" s="24" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="D16" s="25" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="E16" s="24" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11475,16 +11481,16 @@
         <v>27</v>
       </c>
       <c r="B17" s="26" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="C17" s="26" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="D17" s="27" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="E17" s="26" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11492,16 +11498,16 @@
         <v>27</v>
       </c>
       <c r="B18" s="24" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="C18" s="24" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="D18" s="25" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="E18" s="24" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11509,16 +11515,16 @@
         <v>27</v>
       </c>
       <c r="B19" s="26" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="C19" s="26" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="D19" s="27" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="E19" s="26" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11526,16 +11532,16 @@
         <v>27</v>
       </c>
       <c r="B20" s="24" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="C20" s="24" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="D20" s="25" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="E20" s="24" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11543,16 +11549,16 @@
         <v>27</v>
       </c>
       <c r="B21" s="26" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="C21" s="26" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="D21" s="27" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="E21" s="26" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11560,16 +11566,16 @@
         <v>27</v>
       </c>
       <c r="B22" s="24" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="C22" s="24" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="D22" s="25" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="E22" s="24" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11577,16 +11583,16 @@
         <v>27</v>
       </c>
       <c r="B23" s="26" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="C23" s="26" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="D23" s="27" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="E23" s="26" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11594,16 +11600,16 @@
         <v>27</v>
       </c>
       <c r="B24" s="24" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="C24" s="24" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="D24" s="25" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="E24" s="24" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
     </row>
     <row r="25" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11611,16 +11617,16 @@
         <v>27</v>
       </c>
       <c r="B25" s="26" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="C25" s="26" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="D25" s="27" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="E25" s="26" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
     </row>
     <row r="26" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11628,16 +11634,16 @@
         <v>27</v>
       </c>
       <c r="B26" s="24" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="C26" s="24" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="D26" s="25" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="E26" s="24" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
     </row>
     <row r="27" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11645,16 +11651,16 @@
         <v>27</v>
       </c>
       <c r="B27" s="26" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="C27" s="26" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="D27" s="27" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="E27" s="26" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11662,16 +11668,16 @@
         <v>27</v>
       </c>
       <c r="B28" s="24" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="C28" s="24" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="D28" s="25" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="E28" s="24" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
     </row>
     <row r="29" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11679,16 +11685,16 @@
         <v>27</v>
       </c>
       <c r="B29" s="26" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="C29" s="26" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="D29" s="27" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="E29" s="26" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
     </row>
     <row r="30" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11696,16 +11702,16 @@
         <v>27</v>
       </c>
       <c r="B30" s="24" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="C30" s="24" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="D30" s="25" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="E30" s="24" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
     </row>
     <row r="31" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11713,16 +11719,16 @@
         <v>27</v>
       </c>
       <c r="B31" s="26" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="C31" s="26" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="D31" s="27" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="E31" s="26" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
     </row>
     <row r="32" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11730,16 +11736,16 @@
         <v>27</v>
       </c>
       <c r="B32" s="24" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="C32" s="24" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="D32" s="25" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="E32" s="24" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11747,16 +11753,16 @@
         <v>27</v>
       </c>
       <c r="B33" s="26" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="C33" s="26" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="D33" s="27" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="E33" s="26" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
     </row>
     <row r="34" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11764,16 +11770,16 @@
         <v>27</v>
       </c>
       <c r="B34" s="24" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="C34" s="24" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="D34" s="25" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="E34" s="24" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
     </row>
     <row r="35" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11781,16 +11787,16 @@
         <v>27</v>
       </c>
       <c r="B35" s="26" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="C35" s="26" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="D35" s="27" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="E35" s="26" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
     </row>
     <row r="36" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11798,16 +11804,16 @@
         <v>27</v>
       </c>
       <c r="B36" s="24" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="C36" s="24" t="s">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="D36" s="25" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="E36" s="24" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
     </row>
     <row r="37" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11815,16 +11821,16 @@
         <v>27</v>
       </c>
       <c r="B37" s="26" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="C37" s="26" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="D37" s="27" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="E37" s="26" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
     </row>
     <row r="38" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11832,16 +11838,16 @@
         <v>27</v>
       </c>
       <c r="B38" s="24" t="s">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="C38" s="24" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="D38" s="25" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="E38" s="24" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
     </row>
     <row r="39" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11849,16 +11855,16 @@
         <v>27</v>
       </c>
       <c r="B39" s="26" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="C39" s="26" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="D39" s="27" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="E39" s="26" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
     </row>
     <row r="40" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11866,16 +11872,16 @@
         <v>27</v>
       </c>
       <c r="B40" s="24" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="C40" s="24" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="D40" s="25" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="E40" s="24" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
     </row>
     <row r="41" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11883,16 +11889,16 @@
         <v>27</v>
       </c>
       <c r="B41" s="26" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="C41" s="26" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="D41" s="27" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="E41" s="26" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
     </row>
     <row r="42" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11900,16 +11906,16 @@
         <v>27</v>
       </c>
       <c r="B42" s="24" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="C42" s="24" t="s">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="D42" s="25" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="E42" s="24" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
     </row>
     <row r="43" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11917,16 +11923,16 @@
         <v>27</v>
       </c>
       <c r="B43" s="26" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="C43" s="26" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="D43" s="27" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="E43" s="26" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
     </row>
     <row r="44" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11934,16 +11940,16 @@
         <v>27</v>
       </c>
       <c r="B44" s="24" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="C44" s="24" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="D44" s="25" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="E44" s="24" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
     </row>
     <row r="45" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11951,16 +11957,16 @@
         <v>27</v>
       </c>
       <c r="B45" s="26" t="s">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="C45" s="26" t="s">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="D45" s="27" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="E45" s="26" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
     </row>
     <row r="46" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11968,16 +11974,16 @@
         <v>27</v>
       </c>
       <c r="B46" s="24" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="C46" s="24" t="s">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="D46" s="25" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="E46" s="24" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
     </row>
     <row r="47" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11985,16 +11991,16 @@
         <v>27</v>
       </c>
       <c r="B47" s="26" t="s">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="C47" s="26" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="D47" s="27" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="E47" s="26" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
     </row>
     <row r="48" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12002,16 +12008,16 @@
         <v>27</v>
       </c>
       <c r="B48" s="24" t="s">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="C48" s="24" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="D48" s="25" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="E48" s="24" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
     </row>
     <row r="49" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12019,16 +12025,16 @@
         <v>27</v>
       </c>
       <c r="B49" s="26" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="C49" s="26" t="s">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="D49" s="27" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="E49" s="26" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
     </row>
     <row r="50" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12036,16 +12042,16 @@
         <v>27</v>
       </c>
       <c r="B50" s="24" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="C50" s="24" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="D50" s="25" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="E50" s="24" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
     </row>
     <row r="51" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12053,16 +12059,16 @@
         <v>27</v>
       </c>
       <c r="B51" s="26" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="C51" s="26" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="D51" s="27" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="E51" s="26" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
     </row>
     <row r="52" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12070,16 +12076,16 @@
         <v>27</v>
       </c>
       <c r="B52" s="24" t="s">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="C52" s="24" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="D52" s="25" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="E52" s="24" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
     </row>
     <row r="53" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12087,16 +12093,16 @@
         <v>27</v>
       </c>
       <c r="B53" s="26" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="C53" s="26" t="s">
+        <v>772</v>
+      </c>
+      <c r="D53" s="27" t="s">
+        <v>668</v>
+      </c>
+      <c r="E53" s="26" t="s">
         <v>770</v>
-      </c>
-      <c r="D53" s="27" t="s">
-        <v>666</v>
-      </c>
-      <c r="E53" s="26" t="s">
-        <v>768</v>
       </c>
     </row>
     <row r="54" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12104,16 +12110,16 @@
         <v>27</v>
       </c>
       <c r="B54" s="24" t="s">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="C54" s="24" t="s">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="D54" s="25" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="E54" s="24" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
     </row>
     <row r="55" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12121,16 +12127,16 @@
         <v>27</v>
       </c>
       <c r="B55" s="26" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="C55" s="26" t="s">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="D55" s="27" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="E55" s="26" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
     </row>
     <row r="56" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12138,16 +12144,16 @@
         <v>27</v>
       </c>
       <c r="B56" s="24" t="s">
-        <v>775</v>
+        <v>777</v>
       </c>
       <c r="C56" s="24" t="s">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="D56" s="25" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="E56" s="24" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
     </row>
     <row r="57" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12155,16 +12161,16 @@
         <v>27</v>
       </c>
       <c r="B57" s="26" t="s">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="C57" s="26" t="s">
-        <v>778</v>
+        <v>780</v>
       </c>
       <c r="D57" s="27" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="E57" s="26" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
     </row>
     <row r="58" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12172,16 +12178,16 @@
         <v>27</v>
       </c>
       <c r="B58" s="24" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="C58" s="24" t="s">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="D58" s="25" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="E58" s="24" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
     </row>
     <row r="59" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12189,16 +12195,16 @@
         <v>27</v>
       </c>
       <c r="B59" s="26" t="s">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="C59" s="26" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="D59" s="27" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="E59" s="26" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
     </row>
     <row r="60" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12206,16 +12212,16 @@
         <v>27</v>
       </c>
       <c r="B60" s="24" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="C60" s="24" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="D60" s="25" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="E60" s="24" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
     </row>
     <row r="61" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12223,16 +12229,16 @@
         <v>27</v>
       </c>
       <c r="B61" s="26" t="s">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="C61" s="26" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="D61" s="27" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="E61" s="26" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
     </row>
     <row r="62" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12240,16 +12246,16 @@
         <v>27</v>
       </c>
       <c r="B62" s="24" t="s">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="C62" s="24" t="s">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="D62" s="25" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="E62" s="24" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
     </row>
     <row r="63" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12257,16 +12263,16 @@
         <v>27</v>
       </c>
       <c r="B63" s="26" t="s">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="C63" s="26" t="s">
+        <v>793</v>
+      </c>
+      <c r="D63" s="27" t="s">
+        <v>668</v>
+      </c>
+      <c r="E63" s="26" t="s">
         <v>791</v>
-      </c>
-      <c r="D63" s="27" t="s">
-        <v>666</v>
-      </c>
-      <c r="E63" s="26" t="s">
-        <v>789</v>
       </c>
     </row>
     <row r="64" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12274,16 +12280,16 @@
         <v>27</v>
       </c>
       <c r="B64" s="24" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="C64" s="24" t="s">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="D64" s="25" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="E64" s="24" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
     </row>
     <row r="65" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12291,16 +12297,16 @@
         <v>27</v>
       </c>
       <c r="B65" s="26" t="s">
-        <v>794</v>
+        <v>796</v>
       </c>
       <c r="C65" s="26" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="D65" s="27" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="E65" s="26" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
     </row>
     <row r="66" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12308,16 +12314,16 @@
         <v>27</v>
       </c>
       <c r="B66" s="24" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="C66" s="24" t="s">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="D66" s="25" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="E66" s="24" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
     </row>
     <row r="67" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12325,16 +12331,16 @@
         <v>27</v>
       </c>
       <c r="B67" s="26" t="s">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="C67" s="26" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="D67" s="27" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="E67" s="26" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
     </row>
     <row r="68" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12342,16 +12348,16 @@
         <v>27</v>
       </c>
       <c r="B68" s="24" t="s">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="C68" s="24" t="s">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="D68" s="25" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="E68" s="24" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
     </row>
     <row r="69" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12359,16 +12365,16 @@
         <v>27</v>
       </c>
       <c r="B69" s="26" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="C69" s="26" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="D69" s="27" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="E69" s="26" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
     </row>
     <row r="70" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12376,16 +12382,16 @@
         <v>27</v>
       </c>
       <c r="B70" s="24" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="C70" s="24" t="s">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="D70" s="25" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="E70" s="24" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
     </row>
     <row r="71" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12393,16 +12399,16 @@
         <v>27</v>
       </c>
       <c r="B71" s="26" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="C71" s="26" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="D71" s="27" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="E71" s="26" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
     </row>
     <row r="72" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12410,16 +12416,16 @@
         <v>27</v>
       </c>
       <c r="B72" s="24" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="C72" s="24" t="s">
-        <v>809</v>
+        <v>811</v>
       </c>
       <c r="D72" s="25" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="E72" s="24" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
     </row>
     <row r="73" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12427,16 +12433,16 @@
         <v>27</v>
       </c>
       <c r="B73" s="26" t="s">
-        <v>811</v>
+        <v>813</v>
       </c>
       <c r="C73" s="26" t="s">
+        <v>814</v>
+      </c>
+      <c r="D73" s="27" t="s">
+        <v>668</v>
+      </c>
+      <c r="E73" s="26" t="s">
         <v>812</v>
-      </c>
-      <c r="D73" s="27" t="s">
-        <v>666</v>
-      </c>
-      <c r="E73" s="26" t="s">
-        <v>810</v>
       </c>
     </row>
     <row r="74" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12444,16 +12450,16 @@
         <v>27</v>
       </c>
       <c r="B74" s="24" t="s">
-        <v>813</v>
+        <v>815</v>
       </c>
       <c r="C74" s="24" t="s">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="D74" s="25" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="E74" s="24" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
     </row>
     <row r="75" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12461,16 +12467,16 @@
         <v>27</v>
       </c>
       <c r="B75" s="26" t="s">
-        <v>815</v>
+        <v>817</v>
       </c>
       <c r="C75" s="26" t="s">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="D75" s="27" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="E75" s="26" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
     </row>
     <row r="76" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12478,16 +12484,16 @@
         <v>27</v>
       </c>
       <c r="B76" s="24" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="C76" s="24" t="s">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="D76" s="25" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="E76" s="24" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
     </row>
     <row r="77" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12495,16 +12501,16 @@
         <v>27</v>
       </c>
       <c r="B77" s="26" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="C77" s="26" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="D77" s="27" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="E77" s="26" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
     </row>
     <row r="78" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12512,16 +12518,16 @@
         <v>27</v>
       </c>
       <c r="B78" s="24" t="s">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="C78" s="24" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="D78" s="25" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="E78" s="24" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
     </row>
     <row r="79" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12529,16 +12535,16 @@
         <v>27</v>
       </c>
       <c r="B79" s="26" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="C79" s="26" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="D79" s="27" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="E79" s="26" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
     </row>
     <row r="80" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12546,16 +12552,16 @@
         <v>27</v>
       </c>
       <c r="B80" s="24" t="s">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="C80" s="24" t="s">
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="D80" s="25" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="E80" s="24" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
     </row>
     <row r="81" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12563,16 +12569,16 @@
         <v>27</v>
       </c>
       <c r="B81" s="26" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="C81" s="26" t="s">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="D81" s="27" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="E81" s="26" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
     </row>
     <row r="82" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12580,16 +12586,16 @@
         <v>27</v>
       </c>
       <c r="B82" s="24" t="s">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="C82" s="24" t="s">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="D82" s="25" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="E82" s="24" t="s">
-        <v>831</v>
+        <v>833</v>
       </c>
     </row>
     <row r="83" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12597,16 +12603,16 @@
         <v>27</v>
       </c>
       <c r="B83" s="26" t="s">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="C83" s="26" t="s">
+        <v>835</v>
+      </c>
+      <c r="D83" s="27" t="s">
+        <v>668</v>
+      </c>
+      <c r="E83" s="26" t="s">
         <v>833</v>
-      </c>
-      <c r="D83" s="27" t="s">
-        <v>666</v>
-      </c>
-      <c r="E83" s="26" t="s">
-        <v>831</v>
       </c>
     </row>
     <row r="84" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12614,16 +12620,16 @@
         <v>27</v>
       </c>
       <c r="B84" s="24" t="s">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="C84" s="24" t="s">
-        <v>835</v>
+        <v>837</v>
       </c>
       <c r="D84" s="25" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="E84" s="24" t="s">
-        <v>831</v>
+        <v>833</v>
       </c>
     </row>
     <row r="85" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12631,16 +12637,16 @@
         <v>27</v>
       </c>
       <c r="B85" s="26" t="s">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="C85" s="26" t="s">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="D85" s="27" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="E85" s="26" t="s">
-        <v>831</v>
+        <v>833</v>
       </c>
     </row>
     <row r="86" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12648,16 +12654,16 @@
         <v>27</v>
       </c>
       <c r="B86" s="24" t="s">
-        <v>838</v>
+        <v>840</v>
       </c>
       <c r="C86" s="24" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="D86" s="25" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="E86" s="24" t="s">
-        <v>831</v>
+        <v>833</v>
       </c>
     </row>
     <row r="87" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12665,16 +12671,16 @@
         <v>27</v>
       </c>
       <c r="B87" s="26" t="s">
-        <v>840</v>
+        <v>842</v>
       </c>
       <c r="C87" s="26" t="s">
-        <v>841</v>
+        <v>843</v>
       </c>
       <c r="D87" s="27" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="E87" s="26" t="s">
-        <v>831</v>
+        <v>833</v>
       </c>
     </row>
     <row r="88" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12682,16 +12688,16 @@
         <v>27</v>
       </c>
       <c r="B88" s="24" t="s">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="C88" s="24" t="s">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="D88" s="25" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="E88" s="24" t="s">
-        <v>831</v>
+        <v>833</v>
       </c>
     </row>
     <row r="89" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12699,16 +12705,16 @@
         <v>27</v>
       </c>
       <c r="B89" s="26" t="s">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="C89" s="26" t="s">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="D89" s="27" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="E89" s="26" t="s">
-        <v>831</v>
+        <v>833</v>
       </c>
     </row>
     <row r="90" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12716,16 +12722,16 @@
         <v>27</v>
       </c>
       <c r="B90" s="24" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="C90" s="24" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="D90" s="25" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="E90" s="24" t="s">
-        <v>831</v>
+        <v>833</v>
       </c>
     </row>
     <row r="91" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12733,16 +12739,16 @@
         <v>27</v>
       </c>
       <c r="B91" s="26" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="C91" s="26" t="s">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="D91" s="27" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="E91" s="26" t="s">
-        <v>831</v>
+        <v>833</v>
       </c>
     </row>
   </sheetData>

--- a/reports/excel/E2E_Report.xlsx
+++ b/reports/excel/E2E_Report.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2887" uniqueCount="852">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2887" uniqueCount="850">
   <si>
     <t>📊 E2E REPORT - AUTOMATION EXECUTION SUMMARY</t>
   </si>
@@ -97,315 +97,315 @@
     <t>PASSED</t>
   </si>
   <si>
-    <t>2026-08-20 04:37:21</t>
+    <t>2026-08-20 03:51:22</t>
+  </si>
+  <si>
+    <t>TC-SEL-002</t>
+  </si>
+  <si>
+    <t>Block redirect. Display 'Invalid credentials' error message on empty credentials</t>
+  </si>
+  <si>
+    <t>TC-SEL-003</t>
+  </si>
+  <si>
+    <t>Redirect user to homepage dashboard on successful user registration</t>
+  </si>
+  <si>
+    <t>TC-SEL-004</t>
+  </si>
+  <si>
+    <t>Block redirect. Display 'Invalid credentials' on empty password submission</t>
+  </si>
+  <si>
+    <t>TC-SEL-005</t>
+  </si>
+  <si>
+    <t>Redirect user to homepage dashboard on session cookie persistence</t>
+  </si>
+  <si>
+    <t>TC-SEL-006</t>
+  </si>
+  <si>
+    <t>Block redirect. Display 'Invalid credentials' on non-existent username</t>
+  </si>
+  <si>
+    <t>TC-SEL-007</t>
+  </si>
+  <si>
+    <t>Redirect user to homepage dashboard on remembered session state</t>
+  </si>
+  <si>
+    <t>TC-SEL-008</t>
+  </si>
+  <si>
+    <t>Block redirect. Display 'Invalid credentials' on whitespace credentials</t>
+  </si>
+  <si>
+    <t>TC-SEL-009</t>
+  </si>
+  <si>
+    <t>Redirect user to homepage dashboard on Google OAuth SSO fallback</t>
+  </si>
+  <si>
+    <t>TC-SEL-010</t>
+  </si>
+  <si>
+    <t>Block redirect. Display 'Invalid credentials' on password mismatch</t>
+  </si>
+  <si>
+    <t>TC-SEL-011</t>
+  </si>
+  <si>
+    <t>Block redirect. Display 'Invalid credentials' on empty username</t>
+  </si>
+  <si>
+    <t>TC-SEL-012</t>
+  </si>
+  <si>
+    <t>Block redirect. Display 'Invalid credentials' on username under minimum length</t>
+  </si>
+  <si>
+    <t>TC-SEL-013</t>
+  </si>
+  <si>
+    <t>Block redirect. Display 'Invalid credentials' on username exceeding maximum length</t>
+  </si>
+  <si>
+    <t>TC-SEL-014</t>
+  </si>
+  <si>
+    <t>Block redirect. Display 'Invalid credentials' on single-character password</t>
+  </si>
+  <si>
+    <t>TC-SEL-015</t>
+  </si>
+  <si>
+    <t>Block redirect. Display 'Invalid credentials' on special symbol username</t>
+  </si>
+  <si>
+    <t>TC-SEL-016</t>
+  </si>
+  <si>
+    <t>Block redirect. Display 'Invalid credentials' on SQL injection attempt</t>
+  </si>
+  <si>
+    <t>TC-SEL-017</t>
+  </si>
+  <si>
+    <t>Block redirect. Display 'Invalid credentials' on script tag payload</t>
+  </si>
+  <si>
+    <t>TC-SEL-018</t>
+  </si>
+  <si>
+    <t>Block redirect. Display 'Invalid credentials' on null literal string</t>
+  </si>
+  <si>
+    <t>TC-SEL-019</t>
+  </si>
+  <si>
+    <t>Block redirect. Display 'Invalid credentials' on undefined payload</t>
+  </si>
+  <si>
+    <t>TC-SEL-020</t>
+  </si>
+  <si>
+    <t>Block redirect. Display 'Invalid credentials' on wrong password for existing user</t>
+  </si>
+  <si>
+    <t>TC-SEL-021</t>
+  </si>
+  <si>
+    <t>Register new user with valid alphanumeric credentials</t>
+  </si>
+  <si>
+    <t>TC-SEL-022</t>
+  </si>
+  <si>
+    <t>Block registration on duplicate username with user friendly warning</t>
+  </si>
+  <si>
+    <t>TC-SEL-023</t>
+  </si>
+  <si>
+    <t>Register new user with underscore and dot in username</t>
+  </si>
+  <si>
+    <t>TC-SEL-024</t>
+  </si>
+  <si>
+    <t>Register new user with complex password containing symbols</t>
+  </si>
+  <si>
+    <t>TC-SEL-025</t>
+  </si>
+  <si>
+    <t>Block registration on mismatched confirm password</t>
+  </si>
+  <si>
+    <t>TC-SEL-026</t>
+  </si>
+  <si>
+    <t>Register new user and trim leading/trailing whitespace</t>
+  </si>
+  <si>
+    <t>TC-SEL-027</t>
+  </si>
+  <si>
+    <t>Register new user and verify empty reading history initialization</t>
+  </si>
+  <si>
+    <t>TC-SEL-028</t>
+  </si>
+  <si>
+    <t>Register new user and verify empty bookmarks list initialization</t>
+  </si>
+  <si>
+    <t>TC-SEL-029</t>
+  </si>
+  <si>
+    <t>Register new user and verify default theme preference</t>
+  </si>
+  <si>
+    <t>TC-SEL-030</t>
+  </si>
+  <si>
+    <t>Register new user and redirect immediately to personalized feed</t>
+  </si>
+  <si>
+    <t>TC-SEL-031</t>
+  </si>
+  <si>
+    <t>Authenticate valid user and verify session cookie issuance</t>
+  </si>
+  <si>
+    <t>TC-SEL-032</t>
+  </si>
+  <si>
+    <t>Verify session cookie contains HttpOnly security flag</t>
+  </si>
+  <si>
+    <t>TC-SEL-033</t>
+  </si>
+  <si>
+    <t>Verify session cookie contains SameSite=Lax/Strict attribute</t>
+  </si>
+  <si>
+    <t>TC-SEL-034</t>
+  </si>
+  <si>
+    <t>Verify authenticated user can access protected /settings</t>
+  </si>
+  <si>
+    <t>TC-SEL-035</t>
+  </si>
+  <si>
+    <t>Verify authenticated user can access protected /bookmarks</t>
+  </si>
+  <si>
+    <t>TC-SEL-036</t>
+  </si>
+  <si>
+    <t>Verify authenticated user can access protected /history</t>
+  </si>
+  <si>
+    <t>TC-SEL-037</t>
+  </si>
+  <si>
+    <t>Block unauthenticated direct access to /settings</t>
+  </si>
+  <si>
+    <t>TC-SEL-038</t>
+  </si>
+  <si>
+    <t>Block unauthenticated direct access to /bookmarks</t>
+  </si>
+  <si>
+    <t>TC-SEL-039</t>
+  </si>
+  <si>
+    <t>Verify session persistence across multiple HTTP requests</t>
+  </si>
+  <si>
+    <t>TC-SEL-040</t>
+  </si>
+  <si>
+    <t>Verify session state remains valid on page reload</t>
+  </si>
+  <si>
+    <t>TC-SEL-041</t>
+  </si>
+  <si>
+    <t>Verify /logout POST request invalidates active user session</t>
+  </si>
+  <si>
+    <t>TC-SEL-042</t>
+  </si>
+  <si>
+    <t>Redirect user to /login or / after successful logout</t>
+  </si>
+  <si>
+    <t>TC-SEL-043</t>
+  </si>
+  <si>
+    <t>Block back-button caching of protected session pages after logout</t>
+  </si>
+  <si>
+    <t>TC-SEL-044</t>
+  </si>
+  <si>
+    <t>Verify session cookie is cleared or expired upon logout</t>
+  </si>
+  <si>
+    <t>TC-SEL-045</t>
+  </si>
+  <si>
+    <t>Verify calling /api/account after logout returns 401 unauthenticated</t>
+  </si>
+  <si>
+    <t>TC-SEL-046</t>
+  </si>
+  <si>
+    <t>Verify concurrent user logins handled gracefully</t>
+  </si>
+  <si>
+    <t>TC-SEL-047</t>
+  </si>
+  <si>
+    <t>Verify Google OAuth mock callback handles state parameter</t>
+  </si>
+  <si>
+    <t>TC-SEL-048</t>
+  </si>
+  <si>
+    <t>Verify password hashing algorithm uses modern cryptography</t>
+  </si>
+  <si>
+    <t>TC-SEL-049</t>
+  </si>
+  <si>
+    <t>Verify password is never echoed in plain text in response HTML</t>
+  </si>
+  <si>
+    <t>TC-SEL-050</t>
+  </si>
+  <si>
+    <t>Verify auth headers in response prevent unauthorized caching</t>
+  </si>
+  <si>
+    <t>TC-SEL-051</t>
+  </si>
+  <si>
+    <t>Form Discovery Crawler</t>
+  </si>
+  <si>
+    <t>Dynamic Crawler: Discover and index root page forms</t>
   </si>
   <si>
     <t>0.01s</t>
   </si>
   <si>
-    <t>TC-SEL-002</t>
-  </si>
-  <si>
-    <t>Block redirect. Display 'Invalid credentials' error message on empty credentials</t>
-  </si>
-  <si>
-    <t>TC-SEL-003</t>
-  </si>
-  <si>
-    <t>Redirect user to homepage dashboard on successful user registration</t>
-  </si>
-  <si>
-    <t>TC-SEL-004</t>
-  </si>
-  <si>
-    <t>Block redirect. Display 'Invalid credentials' on empty password submission</t>
-  </si>
-  <si>
-    <t>TC-SEL-005</t>
-  </si>
-  <si>
-    <t>Redirect user to homepage dashboard on session cookie persistence</t>
-  </si>
-  <si>
-    <t>TC-SEL-006</t>
-  </si>
-  <si>
-    <t>Block redirect. Display 'Invalid credentials' on non-existent username</t>
-  </si>
-  <si>
-    <t>TC-SEL-007</t>
-  </si>
-  <si>
-    <t>Redirect user to homepage dashboard on remembered session state</t>
-  </si>
-  <si>
-    <t>TC-SEL-008</t>
-  </si>
-  <si>
-    <t>Block redirect. Display 'Invalid credentials' on whitespace credentials</t>
-  </si>
-  <si>
-    <t>TC-SEL-009</t>
-  </si>
-  <si>
-    <t>Redirect user to homepage dashboard on Google OAuth SSO fallback</t>
-  </si>
-  <si>
-    <t>TC-SEL-010</t>
-  </si>
-  <si>
-    <t>Block redirect. Display 'Invalid credentials' on password mismatch</t>
-  </si>
-  <si>
-    <t>TC-SEL-011</t>
-  </si>
-  <si>
-    <t>Block redirect. Display 'Invalid credentials' on empty username</t>
-  </si>
-  <si>
-    <t>TC-SEL-012</t>
-  </si>
-  <si>
-    <t>Block redirect. Display 'Invalid credentials' on username under minimum length</t>
-  </si>
-  <si>
-    <t>TC-SEL-013</t>
-  </si>
-  <si>
-    <t>Block redirect. Display 'Invalid credentials' on username exceeding maximum length</t>
-  </si>
-  <si>
-    <t>TC-SEL-014</t>
-  </si>
-  <si>
-    <t>Block redirect. Display 'Invalid credentials' on single-character password</t>
-  </si>
-  <si>
-    <t>TC-SEL-015</t>
-  </si>
-  <si>
-    <t>Block redirect. Display 'Invalid credentials' on special symbol username</t>
-  </si>
-  <si>
-    <t>TC-SEL-016</t>
-  </si>
-  <si>
-    <t>Block redirect. Display 'Invalid credentials' on SQL injection attempt</t>
-  </si>
-  <si>
-    <t>TC-SEL-017</t>
-  </si>
-  <si>
-    <t>Block redirect. Display 'Invalid credentials' on script tag payload</t>
-  </si>
-  <si>
-    <t>TC-SEL-018</t>
-  </si>
-  <si>
-    <t>Block redirect. Display 'Invalid credentials' on null literal string</t>
-  </si>
-  <si>
-    <t>TC-SEL-019</t>
-  </si>
-  <si>
-    <t>Block redirect. Display 'Invalid credentials' on undefined payload</t>
-  </si>
-  <si>
-    <t>TC-SEL-020</t>
-  </si>
-  <si>
-    <t>Block redirect. Display 'Invalid credentials' on wrong password for existing user</t>
-  </si>
-  <si>
-    <t>TC-SEL-021</t>
-  </si>
-  <si>
-    <t>Register new user with valid alphanumeric credentials</t>
-  </si>
-  <si>
-    <t>TC-SEL-022</t>
-  </si>
-  <si>
-    <t>Block registration on duplicate username with user friendly warning</t>
-  </si>
-  <si>
-    <t>TC-SEL-023</t>
-  </si>
-  <si>
-    <t>Register new user with underscore and dot in username</t>
-  </si>
-  <si>
-    <t>TC-SEL-024</t>
-  </si>
-  <si>
-    <t>Register new user with complex password containing symbols</t>
-  </si>
-  <si>
-    <t>TC-SEL-025</t>
-  </si>
-  <si>
-    <t>Block registration on mismatched confirm password</t>
-  </si>
-  <si>
-    <t>TC-SEL-026</t>
-  </si>
-  <si>
-    <t>Register new user and trim leading/trailing whitespace</t>
-  </si>
-  <si>
-    <t>TC-SEL-027</t>
-  </si>
-  <si>
-    <t>Register new user and verify empty reading history initialization</t>
-  </si>
-  <si>
-    <t>TC-SEL-028</t>
-  </si>
-  <si>
-    <t>Register new user and verify empty bookmarks list initialization</t>
-  </si>
-  <si>
-    <t>TC-SEL-029</t>
-  </si>
-  <si>
-    <t>Register new user and verify default theme preference</t>
-  </si>
-  <si>
-    <t>TC-SEL-030</t>
-  </si>
-  <si>
-    <t>Register new user and redirect immediately to personalized feed</t>
-  </si>
-  <si>
-    <t>TC-SEL-031</t>
-  </si>
-  <si>
-    <t>Authenticate valid user and verify session cookie issuance</t>
-  </si>
-  <si>
-    <t>TC-SEL-032</t>
-  </si>
-  <si>
-    <t>Verify session cookie contains HttpOnly security flag</t>
-  </si>
-  <si>
-    <t>TC-SEL-033</t>
-  </si>
-  <si>
-    <t>Verify session cookie contains SameSite=Lax/Strict attribute</t>
-  </si>
-  <si>
-    <t>TC-SEL-034</t>
-  </si>
-  <si>
-    <t>Verify authenticated user can access protected /settings</t>
-  </si>
-  <si>
-    <t>TC-SEL-035</t>
-  </si>
-  <si>
-    <t>Verify authenticated user can access protected /bookmarks</t>
-  </si>
-  <si>
-    <t>TC-SEL-036</t>
-  </si>
-  <si>
-    <t>Verify authenticated user can access protected /history</t>
-  </si>
-  <si>
-    <t>TC-SEL-037</t>
-  </si>
-  <si>
-    <t>Block unauthenticated direct access to /settings</t>
-  </si>
-  <si>
-    <t>TC-SEL-038</t>
-  </si>
-  <si>
-    <t>Block unauthenticated direct access to /bookmarks</t>
-  </si>
-  <si>
-    <t>TC-SEL-039</t>
-  </si>
-  <si>
-    <t>Verify session persistence across multiple HTTP requests</t>
-  </si>
-  <si>
-    <t>TC-SEL-040</t>
-  </si>
-  <si>
-    <t>Verify session state remains valid on page reload</t>
-  </si>
-  <si>
-    <t>TC-SEL-041</t>
-  </si>
-  <si>
-    <t>Verify /logout POST request invalidates active user session</t>
-  </si>
-  <si>
-    <t>TC-SEL-042</t>
-  </si>
-  <si>
-    <t>Redirect user to /login or / after successful logout</t>
-  </si>
-  <si>
-    <t>TC-SEL-043</t>
-  </si>
-  <si>
-    <t>Block back-button caching of protected session pages after logout</t>
-  </si>
-  <si>
-    <t>TC-SEL-044</t>
-  </si>
-  <si>
-    <t>Verify session cookie is cleared or expired upon logout</t>
-  </si>
-  <si>
-    <t>TC-SEL-045</t>
-  </si>
-  <si>
-    <t>Verify calling /api/account after logout returns 401 unauthenticated</t>
-  </si>
-  <si>
-    <t>TC-SEL-046</t>
-  </si>
-  <si>
-    <t>Verify concurrent user logins handled gracefully</t>
-  </si>
-  <si>
-    <t>TC-SEL-047</t>
-  </si>
-  <si>
-    <t>Verify Google OAuth mock callback handles state parameter</t>
-  </si>
-  <si>
-    <t>TC-SEL-048</t>
-  </si>
-  <si>
-    <t>Verify password hashing algorithm uses modern cryptography</t>
-  </si>
-  <si>
-    <t>TC-SEL-049</t>
-  </si>
-  <si>
-    <t>Verify password is never echoed in plain text in response HTML</t>
-  </si>
-  <si>
-    <t>TC-SEL-050</t>
-  </si>
-  <si>
-    <t>Verify auth headers in response prevent unauthorized caching</t>
-  </si>
-  <si>
-    <t>TC-SEL-051</t>
-  </si>
-  <si>
-    <t>Form Discovery Crawler</t>
-  </si>
-  <si>
-    <t>Dynamic Crawler: Discover and index root page forms</t>
-  </si>
-  <si>
     <t>TC-SEL-052</t>
   </si>
   <si>
@@ -442,16 +442,10 @@
     <t>Dynamic Crawler: Discover and index /roundup synthesis forms</t>
   </si>
   <si>
-    <t>0.06s</t>
-  </si>
-  <si>
     <t>TC-SEL-058</t>
   </si>
   <si>
     <t>Dynamic Crawler: Verify all discovered forms specify valid action URI</t>
-  </si>
-  <si>
-    <t>0.02s</t>
   </si>
   <si>
     <t>TC-SEL-059</t>
@@ -3357,18 +3351,18 @@
         <v>27</v>
       </c>
       <c r="H2" s="15" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="17" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B3" s="18" t="s">
         <v>23</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D3" s="20" t="s">
         <v>25</v>
@@ -3388,13 +3382,13 @@
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B4" s="13" t="s">
         <v>23</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D4" s="15" t="s">
         <v>25</v>
@@ -3414,13 +3408,13 @@
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="17" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B5" s="18" t="s">
         <v>23</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D5" s="20" t="s">
         <v>25</v>
@@ -3440,13 +3434,13 @@
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B6" s="13" t="s">
         <v>23</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D6" s="15" t="s">
         <v>25</v>
@@ -3466,13 +3460,13 @@
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="17" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B7" s="18" t="s">
         <v>23</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D7" s="20" t="s">
         <v>25</v>
@@ -3492,13 +3486,13 @@
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B8" s="13" t="s">
         <v>23</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D8" s="15" t="s">
         <v>25</v>
@@ -3518,13 +3512,13 @@
     </row>
     <row r="9" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B9" s="18" t="s">
         <v>23</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D9" s="20" t="s">
         <v>25</v>
@@ -3544,13 +3538,13 @@
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B10" s="13" t="s">
         <v>23</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D10" s="15" t="s">
         <v>25</v>
@@ -3570,13 +3564,13 @@
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B11" s="18" t="s">
         <v>23</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D11" s="20" t="s">
         <v>25</v>
@@ -3596,13 +3590,13 @@
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B12" s="13" t="s">
         <v>23</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D12" s="15" t="s">
         <v>25</v>
@@ -3617,18 +3611,18 @@
         <v>27</v>
       </c>
       <c r="H12" s="15" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="17" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B13" s="18" t="s">
         <v>23</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D13" s="20" t="s">
         <v>25</v>
@@ -3648,13 +3642,13 @@
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B14" s="13" t="s">
         <v>23</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D14" s="15" t="s">
         <v>25</v>
@@ -3674,13 +3668,13 @@
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="17" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B15" s="18" t="s">
         <v>23</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D15" s="20" t="s">
         <v>25</v>
@@ -3700,13 +3694,13 @@
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B16" s="13" t="s">
         <v>23</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D16" s="15" t="s">
         <v>25</v>
@@ -3726,13 +3720,13 @@
     </row>
     <row r="17" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="17" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B17" s="18" t="s">
         <v>23</v>
       </c>
       <c r="C17" s="19" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D17" s="20" t="s">
         <v>25</v>
@@ -3752,13 +3746,13 @@
     </row>
     <row r="18" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B18" s="13" t="s">
         <v>23</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D18" s="15" t="s">
         <v>25</v>
@@ -3778,13 +3772,13 @@
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="17" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B19" s="18" t="s">
         <v>23</v>
       </c>
       <c r="C19" s="19" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D19" s="20" t="s">
         <v>25</v>
@@ -3804,13 +3798,13 @@
     </row>
     <row r="20" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="12" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B20" s="13" t="s">
         <v>23</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D20" s="15" t="s">
         <v>25</v>
@@ -3830,13 +3824,13 @@
     </row>
     <row r="21" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="17" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B21" s="18" t="s">
         <v>23</v>
       </c>
       <c r="C21" s="19" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D21" s="20" t="s">
         <v>25</v>
@@ -3856,13 +3850,13 @@
     </row>
     <row r="22" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="12" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B22" s="13" t="s">
         <v>23</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D22" s="15" t="s">
         <v>25</v>
@@ -3882,13 +3876,13 @@
     </row>
     <row r="23" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="17" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B23" s="18" t="s">
         <v>23</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D23" s="20" t="s">
         <v>25</v>
@@ -3908,13 +3902,13 @@
     </row>
     <row r="24" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B24" s="13" t="s">
         <v>23</v>
       </c>
       <c r="C24" s="14" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D24" s="15" t="s">
         <v>25</v>
@@ -3934,13 +3928,13 @@
     </row>
     <row r="25" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="17" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B25" s="18" t="s">
         <v>23</v>
       </c>
       <c r="C25" s="19" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D25" s="20" t="s">
         <v>25</v>
@@ -3960,13 +3954,13 @@
     </row>
     <row r="26" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="12" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B26" s="13" t="s">
         <v>23</v>
       </c>
       <c r="C26" s="14" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D26" s="15" t="s">
         <v>25</v>
@@ -3986,13 +3980,13 @@
     </row>
     <row r="27" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="17" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B27" s="18" t="s">
         <v>23</v>
       </c>
       <c r="C27" s="19" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D27" s="20" t="s">
         <v>25</v>
@@ -4012,13 +4006,13 @@
     </row>
     <row r="28" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="12" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B28" s="13" t="s">
         <v>23</v>
       </c>
       <c r="C28" s="14" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D28" s="15" t="s">
         <v>25</v>
@@ -4038,13 +4032,13 @@
     </row>
     <row r="29" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="17" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B29" s="18" t="s">
         <v>23</v>
       </c>
       <c r="C29" s="19" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D29" s="20" t="s">
         <v>25</v>
@@ -4064,13 +4058,13 @@
     </row>
     <row r="30" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="12" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B30" s="13" t="s">
         <v>23</v>
       </c>
       <c r="C30" s="14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D30" s="15" t="s">
         <v>25</v>
@@ -4090,13 +4084,13 @@
     </row>
     <row r="31" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B31" s="18" t="s">
         <v>23</v>
       </c>
       <c r="C31" s="19" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D31" s="20" t="s">
         <v>25</v>
@@ -4116,13 +4110,13 @@
     </row>
     <row r="32" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="12" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B32" s="13" t="s">
         <v>23</v>
       </c>
       <c r="C32" s="14" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D32" s="15" t="s">
         <v>25</v>
@@ -4142,13 +4136,13 @@
     </row>
     <row r="33" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="17" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B33" s="18" t="s">
         <v>23</v>
       </c>
       <c r="C33" s="19" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D33" s="20" t="s">
         <v>25</v>
@@ -4168,13 +4162,13 @@
     </row>
     <row r="34" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="12" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B34" s="13" t="s">
         <v>23</v>
       </c>
       <c r="C34" s="14" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D34" s="15" t="s">
         <v>25</v>
@@ -4194,13 +4188,13 @@
     </row>
     <row r="35" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="17" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B35" s="18" t="s">
         <v>23</v>
       </c>
       <c r="C35" s="19" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D35" s="20" t="s">
         <v>25</v>
@@ -4220,13 +4214,13 @@
     </row>
     <row r="36" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="12" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B36" s="13" t="s">
         <v>23</v>
       </c>
       <c r="C36" s="14" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D36" s="15" t="s">
         <v>25</v>
@@ -4246,13 +4240,13 @@
     </row>
     <row r="37" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="17" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B37" s="18" t="s">
         <v>23</v>
       </c>
       <c r="C37" s="19" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D37" s="20" t="s">
         <v>25</v>
@@ -4272,13 +4266,13 @@
     </row>
     <row r="38" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="12" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B38" s="13" t="s">
         <v>23</v>
       </c>
       <c r="C38" s="14" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D38" s="15" t="s">
         <v>25</v>
@@ -4298,13 +4292,13 @@
     </row>
     <row r="39" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="17" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B39" s="18" t="s">
         <v>23</v>
       </c>
       <c r="C39" s="19" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D39" s="20" t="s">
         <v>25</v>
@@ -4324,13 +4318,13 @@
     </row>
     <row r="40" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="12" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B40" s="13" t="s">
         <v>23</v>
       </c>
       <c r="C40" s="14" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D40" s="15" t="s">
         <v>25</v>
@@ -4350,13 +4344,13 @@
     </row>
     <row r="41" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="17" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B41" s="18" t="s">
         <v>23</v>
       </c>
       <c r="C41" s="19" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D41" s="20" t="s">
         <v>25</v>
@@ -4376,13 +4370,13 @@
     </row>
     <row r="42" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="12" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B42" s="13" t="s">
         <v>23</v>
       </c>
       <c r="C42" s="14" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D42" s="15" t="s">
         <v>25</v>
@@ -4402,13 +4396,13 @@
     </row>
     <row r="43" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="17" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B43" s="18" t="s">
         <v>23</v>
       </c>
       <c r="C43" s="19" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D43" s="20" t="s">
         <v>25</v>
@@ -4428,13 +4422,13 @@
     </row>
     <row r="44" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="12" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B44" s="13" t="s">
         <v>23</v>
       </c>
       <c r="C44" s="14" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D44" s="15" t="s">
         <v>25</v>
@@ -4454,13 +4448,13 @@
     </row>
     <row r="45" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="17" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B45" s="18" t="s">
         <v>23</v>
       </c>
       <c r="C45" s="19" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D45" s="20" t="s">
         <v>25</v>
@@ -4480,13 +4474,13 @@
     </row>
     <row r="46" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="12" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B46" s="13" t="s">
         <v>23</v>
       </c>
       <c r="C46" s="14" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D46" s="15" t="s">
         <v>25</v>
@@ -4506,13 +4500,13 @@
     </row>
     <row r="47" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="17" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B47" s="18" t="s">
         <v>23</v>
       </c>
       <c r="C47" s="19" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D47" s="20" t="s">
         <v>25</v>
@@ -4532,13 +4526,13 @@
     </row>
     <row r="48" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A48" s="12" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B48" s="13" t="s">
         <v>23</v>
       </c>
       <c r="C48" s="14" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D48" s="15" t="s">
         <v>25</v>
@@ -4558,13 +4552,13 @@
     </row>
     <row r="49" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="17" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B49" s="18" t="s">
         <v>23</v>
       </c>
       <c r="C49" s="19" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D49" s="20" t="s">
         <v>25</v>
@@ -4584,13 +4578,13 @@
     </row>
     <row r="50" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="12" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B50" s="13" t="s">
         <v>23</v>
       </c>
       <c r="C50" s="14" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D50" s="15" t="s">
         <v>25</v>
@@ -4610,13 +4604,13 @@
     </row>
     <row r="51" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="17" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B51" s="18" t="s">
         <v>23</v>
       </c>
       <c r="C51" s="19" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D51" s="20" t="s">
         <v>25</v>
@@ -4636,28 +4630,28 @@
     </row>
     <row r="52" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A52" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="B52" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="B52" s="13" t="s">
+      <c r="C52" s="14" t="s">
         <v>128</v>
       </c>
-      <c r="C52" s="14" t="s">
+      <c r="D52" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="E52" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="F52" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="G52" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="H52" s="15" t="s">
         <v>129</v>
-      </c>
-      <c r="D52" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="E52" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="F52" s="15" t="s">
-        <v>27</v>
-      </c>
-      <c r="G52" s="15" t="s">
-        <v>27</v>
-      </c>
-      <c r="H52" s="15" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="53" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
@@ -4665,7 +4659,7 @@
         <v>130</v>
       </c>
       <c r="B53" s="18" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C53" s="19" t="s">
         <v>131</v>
@@ -4683,7 +4677,7 @@
         <v>27</v>
       </c>
       <c r="H53" s="20" t="s">
-        <v>28</v>
+        <v>129</v>
       </c>
     </row>
     <row r="54" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
@@ -4691,7 +4685,7 @@
         <v>132</v>
       </c>
       <c r="B54" s="13" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C54" s="14" t="s">
         <v>133</v>
@@ -4709,7 +4703,7 @@
         <v>27</v>
       </c>
       <c r="H54" s="15" t="s">
-        <v>28</v>
+        <v>129</v>
       </c>
     </row>
     <row r="55" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
@@ -4717,7 +4711,7 @@
         <v>134</v>
       </c>
       <c r="B55" s="18" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C55" s="19" t="s">
         <v>135</v>
@@ -4735,7 +4729,7 @@
         <v>27</v>
       </c>
       <c r="H55" s="20" t="s">
-        <v>28</v>
+        <v>129</v>
       </c>
     </row>
     <row r="56" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
@@ -4743,7 +4737,7 @@
         <v>136</v>
       </c>
       <c r="B56" s="13" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C56" s="14" t="s">
         <v>137</v>
@@ -4761,7 +4755,7 @@
         <v>27</v>
       </c>
       <c r="H56" s="15" t="s">
-        <v>28</v>
+        <v>129</v>
       </c>
     </row>
     <row r="57" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
@@ -4769,7 +4763,7 @@
         <v>138</v>
       </c>
       <c r="B57" s="18" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C57" s="19" t="s">
         <v>139</v>
@@ -4787,7 +4781,7 @@
         <v>27</v>
       </c>
       <c r="H57" s="20" t="s">
-        <v>28</v>
+        <v>129</v>
       </c>
     </row>
     <row r="58" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
@@ -4795,7 +4789,7 @@
         <v>140</v>
       </c>
       <c r="B58" s="13" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C58" s="14" t="s">
         <v>141</v>
@@ -4813,19 +4807,19 @@
         <v>27</v>
       </c>
       <c r="H58" s="15" t="s">
-        <v>142</v>
+        <v>129</v>
       </c>
     </row>
     <row r="59" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="17" t="s">
+        <v>142</v>
+      </c>
+      <c r="B59" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="C59" s="19" t="s">
         <v>143</v>
       </c>
-      <c r="B59" s="18" t="s">
-        <v>128</v>
-      </c>
-      <c r="C59" s="19" t="s">
-        <v>144</v>
-      </c>
       <c r="D59" s="20" t="s">
         <v>25</v>
       </c>
@@ -4839,18 +4833,18 @@
         <v>27</v>
       </c>
       <c r="H59" s="20" t="s">
-        <v>145</v>
+        <v>129</v>
       </c>
     </row>
     <row r="60" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="12" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B60" s="13" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C60" s="14" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="D60" s="15" t="s">
         <v>25</v>
@@ -4865,18 +4859,18 @@
         <v>27</v>
       </c>
       <c r="H60" s="15" t="s">
-        <v>28</v>
+        <v>129</v>
       </c>
     </row>
     <row r="61" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A61" s="17" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B61" s="18" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C61" s="19" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D61" s="20" t="s">
         <v>25</v>
@@ -4891,18 +4885,18 @@
         <v>27</v>
       </c>
       <c r="H61" s="20" t="s">
-        <v>28</v>
+        <v>129</v>
       </c>
     </row>
     <row r="62" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A62" s="12" t="s">
+        <v>148</v>
+      </c>
+      <c r="B62" s="13" t="s">
+        <v>149</v>
+      </c>
+      <c r="C62" s="14" t="s">
         <v>150</v>
-      </c>
-      <c r="B62" s="13" t="s">
-        <v>151</v>
-      </c>
-      <c r="C62" s="14" t="s">
-        <v>152</v>
       </c>
       <c r="D62" s="15" t="s">
         <v>25</v>
@@ -4922,13 +4916,13 @@
     </row>
     <row r="63" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="17" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B63" s="18" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C63" s="19" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D63" s="20" t="s">
         <v>25</v>
@@ -4948,13 +4942,13 @@
     </row>
     <row r="64" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A64" s="12" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B64" s="13" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C64" s="14" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D64" s="15" t="s">
         <v>25</v>
@@ -4974,13 +4968,13 @@
     </row>
     <row r="65" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65" s="17" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B65" s="18" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C65" s="19" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D65" s="20" t="s">
         <v>25</v>
@@ -5000,13 +4994,13 @@
     </row>
     <row r="66" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="12" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B66" s="13" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C66" s="14" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D66" s="15" t="s">
         <v>25</v>
@@ -5026,13 +5020,13 @@
     </row>
     <row r="67" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A67" s="17" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B67" s="18" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C67" s="19" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D67" s="20" t="s">
         <v>25</v>
@@ -5052,13 +5046,13 @@
     </row>
     <row r="68" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A68" s="12" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B68" s="13" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C68" s="14" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="D68" s="15" t="s">
         <v>25</v>
@@ -5078,13 +5072,13 @@
     </row>
     <row r="69" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A69" s="17" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B69" s="18" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C69" s="19" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D69" s="20" t="s">
         <v>25</v>
@@ -5104,13 +5098,13 @@
     </row>
     <row r="70" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A70" s="12" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B70" s="13" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C70" s="14" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="D70" s="15" t="s">
         <v>25</v>
@@ -5130,13 +5124,13 @@
     </row>
     <row r="71" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A71" s="17" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B71" s="18" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C71" s="19" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D71" s="20" t="s">
         <v>25</v>
@@ -5156,13 +5150,13 @@
     </row>
     <row r="72" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A72" s="12" t="s">
+        <v>169</v>
+      </c>
+      <c r="B72" s="13" t="s">
+        <v>170</v>
+      </c>
+      <c r="C72" s="14" t="s">
         <v>171</v>
-      </c>
-      <c r="B72" s="13" t="s">
-        <v>172</v>
-      </c>
-      <c r="C72" s="14" t="s">
-        <v>173</v>
       </c>
       <c r="D72" s="15" t="s">
         <v>25</v>
@@ -5182,13 +5176,13 @@
     </row>
     <row r="73" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A73" s="17" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B73" s="18" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C73" s="19" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D73" s="20" t="s">
         <v>25</v>
@@ -5208,13 +5202,13 @@
     </row>
     <row r="74" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A74" s="12" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B74" s="13" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C74" s="14" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D74" s="15" t="s">
         <v>25</v>
@@ -5234,13 +5228,13 @@
     </row>
     <row r="75" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A75" s="17" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B75" s="18" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C75" s="19" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D75" s="20" t="s">
         <v>25</v>
@@ -5260,13 +5254,13 @@
     </row>
     <row r="76" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A76" s="12" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B76" s="13" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C76" s="14" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D76" s="15" t="s">
         <v>25</v>
@@ -5286,13 +5280,13 @@
     </row>
     <row r="77" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A77" s="17" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B77" s="18" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C77" s="19" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D77" s="20" t="s">
         <v>25</v>
@@ -5312,13 +5306,13 @@
     </row>
     <row r="78" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A78" s="12" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B78" s="13" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C78" s="14" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D78" s="15" t="s">
         <v>25</v>
@@ -5338,13 +5332,13 @@
     </row>
     <row r="79" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A79" s="17" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B79" s="18" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C79" s="19" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D79" s="20" t="s">
         <v>25</v>
@@ -5364,13 +5358,13 @@
     </row>
     <row r="80" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A80" s="12" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B80" s="13" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C80" s="14" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D80" s="15" t="s">
         <v>25</v>
@@ -5390,13 +5384,13 @@
     </row>
     <row r="81" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A81" s="17" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B81" s="18" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C81" s="19" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D81" s="20" t="s">
         <v>25</v>
@@ -5416,13 +5410,13 @@
     </row>
     <row r="82" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A82" s="12" t="s">
+        <v>190</v>
+      </c>
+      <c r="B82" s="13" t="s">
+        <v>191</v>
+      </c>
+      <c r="C82" s="14" t="s">
         <v>192</v>
-      </c>
-      <c r="B82" s="13" t="s">
-        <v>193</v>
-      </c>
-      <c r="C82" s="14" t="s">
-        <v>194</v>
       </c>
       <c r="D82" s="15" t="s">
         <v>25</v>
@@ -5442,13 +5436,13 @@
     </row>
     <row r="83" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A83" s="17" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B83" s="18" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C83" s="19" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D83" s="20" t="s">
         <v>25</v>
@@ -5468,13 +5462,13 @@
     </row>
     <row r="84" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A84" s="12" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B84" s="13" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C84" s="14" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D84" s="15" t="s">
         <v>25</v>
@@ -5494,13 +5488,13 @@
     </row>
     <row r="85" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A85" s="17" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B85" s="18" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C85" s="19" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D85" s="20" t="s">
         <v>25</v>
@@ -5520,13 +5514,13 @@
     </row>
     <row r="86" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A86" s="12" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B86" s="13" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C86" s="14" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D86" s="15" t="s">
         <v>25</v>
@@ -5546,13 +5540,13 @@
     </row>
     <row r="87" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A87" s="17" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B87" s="18" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C87" s="19" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D87" s="20" t="s">
         <v>25</v>
@@ -5572,13 +5566,13 @@
     </row>
     <row r="88" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A88" s="12" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B88" s="13" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C88" s="14" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D88" s="15" t="s">
         <v>25</v>
@@ -5598,13 +5592,13 @@
     </row>
     <row r="89" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A89" s="17" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B89" s="18" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C89" s="19" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="D89" s="20" t="s">
         <v>25</v>
@@ -5624,13 +5618,13 @@
     </row>
     <row r="90" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A90" s="12" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B90" s="13" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C90" s="14" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D90" s="15" t="s">
         <v>25</v>
@@ -5650,13 +5644,13 @@
     </row>
     <row r="91" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A91" s="17" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B91" s="18" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C91" s="19" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="D91" s="20" t="s">
         <v>25</v>
@@ -5676,13 +5670,13 @@
     </row>
     <row r="92" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A92" s="12" t="s">
+        <v>211</v>
+      </c>
+      <c r="B92" s="13" t="s">
+        <v>212</v>
+      </c>
+      <c r="C92" s="14" t="s">
         <v>213</v>
-      </c>
-      <c r="B92" s="13" t="s">
-        <v>214</v>
-      </c>
-      <c r="C92" s="14" t="s">
-        <v>215</v>
       </c>
       <c r="D92" s="15" t="s">
         <v>25</v>
@@ -5702,13 +5696,13 @@
     </row>
     <row r="93" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A93" s="17" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B93" s="18" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C93" s="19" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="D93" s="20" t="s">
         <v>25</v>
@@ -5728,13 +5722,13 @@
     </row>
     <row r="94" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A94" s="12" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B94" s="13" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C94" s="14" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="D94" s="15" t="s">
         <v>25</v>
@@ -5754,13 +5748,13 @@
     </row>
     <row r="95" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A95" s="17" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B95" s="18" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C95" s="19" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D95" s="20" t="s">
         <v>25</v>
@@ -5780,13 +5774,13 @@
     </row>
     <row r="96" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A96" s="12" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B96" s="13" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C96" s="14" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D96" s="15" t="s">
         <v>25</v>
@@ -5806,13 +5800,13 @@
     </row>
     <row r="97" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A97" s="17" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B97" s="18" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C97" s="19" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="D97" s="20" t="s">
         <v>25</v>
@@ -5832,13 +5826,13 @@
     </row>
     <row r="98" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A98" s="12" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B98" s="13" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C98" s="14" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D98" s="15" t="s">
         <v>25</v>
@@ -5858,13 +5852,13 @@
     </row>
     <row r="99" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A99" s="17" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B99" s="18" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C99" s="19" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="D99" s="20" t="s">
         <v>25</v>
@@ -5884,13 +5878,13 @@
     </row>
     <row r="100" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A100" s="12" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B100" s="13" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C100" s="14" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="D100" s="15" t="s">
         <v>25</v>
@@ -5910,13 +5904,13 @@
     </row>
     <row r="101" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A101" s="17" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B101" s="18" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C101" s="19" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="D101" s="20" t="s">
         <v>25</v>
@@ -5936,13 +5930,13 @@
     </row>
     <row r="102" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A102" s="12" t="s">
+        <v>232</v>
+      </c>
+      <c r="B102" s="13" t="s">
+        <v>233</v>
+      </c>
+      <c r="C102" s="14" t="s">
         <v>234</v>
-      </c>
-      <c r="B102" s="13" t="s">
-        <v>235</v>
-      </c>
-      <c r="C102" s="14" t="s">
-        <v>236</v>
       </c>
       <c r="D102" s="15" t="s">
         <v>25</v>
@@ -5962,13 +5956,13 @@
     </row>
     <row r="103" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A103" s="17" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B103" s="18" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C103" s="19" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="D103" s="20" t="s">
         <v>25</v>
@@ -5988,13 +5982,13 @@
     </row>
     <row r="104" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A104" s="12" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B104" s="13" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C104" s="14" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="D104" s="15" t="s">
         <v>25</v>
@@ -6014,13 +6008,13 @@
     </row>
     <row r="105" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A105" s="17" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B105" s="18" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C105" s="19" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="D105" s="20" t="s">
         <v>25</v>
@@ -6040,13 +6034,13 @@
     </row>
     <row r="106" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A106" s="12" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B106" s="13" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C106" s="14" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D106" s="15" t="s">
         <v>25</v>
@@ -6066,13 +6060,13 @@
     </row>
     <row r="107" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A107" s="17" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B107" s="18" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C107" s="19" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="D107" s="20" t="s">
         <v>25</v>
@@ -6092,13 +6086,13 @@
     </row>
     <row r="108" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A108" s="12" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B108" s="13" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C108" s="14" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="D108" s="15" t="s">
         <v>25</v>
@@ -6118,13 +6112,13 @@
     </row>
     <row r="109" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A109" s="17" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B109" s="18" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C109" s="19" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="D109" s="20" t="s">
         <v>25</v>
@@ -6144,13 +6138,13 @@
     </row>
     <row r="110" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A110" s="12" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B110" s="13" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C110" s="14" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="D110" s="15" t="s">
         <v>25</v>
@@ -6170,13 +6164,13 @@
     </row>
     <row r="111" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A111" s="17" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B111" s="18" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C111" s="19" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="D111" s="20" t="s">
         <v>25</v>
@@ -6196,13 +6190,13 @@
     </row>
     <row r="112" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A112" s="12" t="s">
+        <v>253</v>
+      </c>
+      <c r="B112" s="13" t="s">
+        <v>254</v>
+      </c>
+      <c r="C112" s="14" t="s">
         <v>255</v>
-      </c>
-      <c r="B112" s="13" t="s">
-        <v>256</v>
-      </c>
-      <c r="C112" s="14" t="s">
-        <v>257</v>
       </c>
       <c r="D112" s="15" t="s">
         <v>25</v>
@@ -6222,13 +6216,13 @@
     </row>
     <row r="113" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A113" s="17" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="B113" s="18" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C113" s="19" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D113" s="20" t="s">
         <v>25</v>
@@ -6248,13 +6242,13 @@
     </row>
     <row r="114" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A114" s="12" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B114" s="13" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C114" s="14" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D114" s="15" t="s">
         <v>25</v>
@@ -6274,13 +6268,13 @@
     </row>
     <row r="115" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A115" s="17" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B115" s="18" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C115" s="19" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D115" s="20" t="s">
         <v>25</v>
@@ -6300,13 +6294,13 @@
     </row>
     <row r="116" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A116" s="12" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B116" s="13" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C116" s="14" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="D116" s="15" t="s">
         <v>25</v>
@@ -6326,13 +6320,13 @@
     </row>
     <row r="117" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A117" s="17" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B117" s="18" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C117" s="19" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="D117" s="20" t="s">
         <v>25</v>
@@ -6352,13 +6346,13 @@
     </row>
     <row r="118" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A118" s="12" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B118" s="13" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C118" s="14" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D118" s="15" t="s">
         <v>25</v>
@@ -6378,13 +6372,13 @@
     </row>
     <row r="119" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A119" s="17" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B119" s="18" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C119" s="19" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="D119" s="20" t="s">
         <v>25</v>
@@ -6404,13 +6398,13 @@
     </row>
     <row r="120" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A120" s="12" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B120" s="13" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C120" s="14" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="D120" s="15" t="s">
         <v>25</v>
@@ -6430,13 +6424,13 @@
     </row>
     <row r="121" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A121" s="17" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B121" s="18" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C121" s="19" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="D121" s="20" t="s">
         <v>25</v>
@@ -6456,13 +6450,13 @@
     </row>
     <row r="122" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A122" s="12" t="s">
+        <v>274</v>
+      </c>
+      <c r="B122" s="13" t="s">
+        <v>275</v>
+      </c>
+      <c r="C122" s="14" t="s">
         <v>276</v>
-      </c>
-      <c r="B122" s="13" t="s">
-        <v>277</v>
-      </c>
-      <c r="C122" s="14" t="s">
-        <v>278</v>
       </c>
       <c r="D122" s="15" t="s">
         <v>25</v>
@@ -6482,13 +6476,13 @@
     </row>
     <row r="123" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A123" s="17" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="B123" s="18" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C123" s="19" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="D123" s="20" t="s">
         <v>25</v>
@@ -6508,13 +6502,13 @@
     </row>
     <row r="124" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A124" s="12" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B124" s="13" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C124" s="14" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="D124" s="15" t="s">
         <v>25</v>
@@ -6534,13 +6528,13 @@
     </row>
     <row r="125" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A125" s="17" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="B125" s="18" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C125" s="19" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="D125" s="20" t="s">
         <v>25</v>
@@ -6560,13 +6554,13 @@
     </row>
     <row r="126" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A126" s="12" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B126" s="13" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C126" s="14" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="D126" s="15" t="s">
         <v>25</v>
@@ -6586,13 +6580,13 @@
     </row>
     <row r="127" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A127" s="17" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B127" s="18" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C127" s="19" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="D127" s="20" t="s">
         <v>25</v>
@@ -6612,13 +6606,13 @@
     </row>
     <row r="128" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A128" s="12" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B128" s="13" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C128" s="14" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="D128" s="15" t="s">
         <v>25</v>
@@ -6638,13 +6632,13 @@
     </row>
     <row r="129" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A129" s="17" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B129" s="18" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C129" s="19" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="D129" s="20" t="s">
         <v>25</v>
@@ -6664,13 +6658,13 @@
     </row>
     <row r="130" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A130" s="12" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B130" s="13" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C130" s="14" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="D130" s="15" t="s">
         <v>25</v>
@@ -6690,13 +6684,13 @@
     </row>
     <row r="131" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A131" s="17" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B131" s="18" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C131" s="19" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="D131" s="20" t="s">
         <v>25</v>
@@ -6716,13 +6710,13 @@
     </row>
     <row r="132" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A132" s="12" t="s">
+        <v>295</v>
+      </c>
+      <c r="B132" s="13" t="s">
+        <v>296</v>
+      </c>
+      <c r="C132" s="14" t="s">
         <v>297</v>
-      </c>
-      <c r="B132" s="13" t="s">
-        <v>298</v>
-      </c>
-      <c r="C132" s="14" t="s">
-        <v>299</v>
       </c>
       <c r="D132" s="15" t="s">
         <v>25</v>
@@ -6742,13 +6736,13 @@
     </row>
     <row r="133" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A133" s="17" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B133" s="18" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C133" s="19" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="D133" s="20" t="s">
         <v>25</v>
@@ -6768,13 +6762,13 @@
     </row>
     <row r="134" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A134" s="12" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="B134" s="13" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C134" s="14" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="D134" s="15" t="s">
         <v>25</v>
@@ -6794,13 +6788,13 @@
     </row>
     <row r="135" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A135" s="17" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B135" s="18" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C135" s="19" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="D135" s="20" t="s">
         <v>25</v>
@@ -6820,13 +6814,13 @@
     </row>
     <row r="136" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A136" s="12" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="B136" s="13" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C136" s="14" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="D136" s="15" t="s">
         <v>25</v>
@@ -6846,13 +6840,13 @@
     </row>
     <row r="137" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A137" s="17" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="B137" s="18" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C137" s="19" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="D137" s="20" t="s">
         <v>25</v>
@@ -6872,13 +6866,13 @@
     </row>
     <row r="138" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A138" s="12" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="B138" s="13" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C138" s="14" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="D138" s="15" t="s">
         <v>25</v>
@@ -6898,13 +6892,13 @@
     </row>
     <row r="139" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A139" s="17" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B139" s="18" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C139" s="19" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="D139" s="20" t="s">
         <v>25</v>
@@ -6924,13 +6918,13 @@
     </row>
     <row r="140" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A140" s="12" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B140" s="13" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C140" s="14" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="D140" s="15" t="s">
         <v>25</v>
@@ -6950,13 +6944,13 @@
     </row>
     <row r="141" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A141" s="17" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B141" s="18" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C141" s="19" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D141" s="20" t="s">
         <v>25</v>
@@ -6976,13 +6970,13 @@
     </row>
     <row r="142" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A142" s="12" t="s">
+        <v>316</v>
+      </c>
+      <c r="B142" s="13" t="s">
+        <v>317</v>
+      </c>
+      <c r="C142" s="14" t="s">
         <v>318</v>
-      </c>
-      <c r="B142" s="13" t="s">
-        <v>319</v>
-      </c>
-      <c r="C142" s="14" t="s">
-        <v>320</v>
       </c>
       <c r="D142" s="15" t="s">
         <v>25</v>
@@ -7002,13 +6996,13 @@
     </row>
     <row r="143" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A143" s="17" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="B143" s="18" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C143" s="19" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="D143" s="20" t="s">
         <v>25</v>
@@ -7028,13 +7022,13 @@
     </row>
     <row r="144" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A144" s="12" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="B144" s="13" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C144" s="14" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D144" s="15" t="s">
         <v>25</v>
@@ -7054,13 +7048,13 @@
     </row>
     <row r="145" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A145" s="17" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="B145" s="18" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C145" s="19" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="D145" s="20" t="s">
         <v>25</v>
@@ -7080,13 +7074,13 @@
     </row>
     <row r="146" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A146" s="12" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B146" s="13" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C146" s="14" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D146" s="15" t="s">
         <v>25</v>
@@ -7106,13 +7100,13 @@
     </row>
     <row r="147" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A147" s="17" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B147" s="18" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C147" s="19" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="D147" s="20" t="s">
         <v>25</v>
@@ -7132,13 +7126,13 @@
     </row>
     <row r="148" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A148" s="12" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B148" s="13" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C148" s="14" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="D148" s="15" t="s">
         <v>25</v>
@@ -7158,13 +7152,13 @@
     </row>
     <row r="149" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A149" s="17" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B149" s="18" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C149" s="19" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="D149" s="20" t="s">
         <v>25</v>
@@ -7184,13 +7178,13 @@
     </row>
     <row r="150" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A150" s="12" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="B150" s="13" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C150" s="14" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="D150" s="15" t="s">
         <v>25</v>
@@ -7210,13 +7204,13 @@
     </row>
     <row r="151" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A151" s="17" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="B151" s="18" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C151" s="19" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D151" s="20" t="s">
         <v>25</v>
@@ -7236,13 +7230,13 @@
     </row>
     <row r="152" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A152" s="12" t="s">
+        <v>337</v>
+      </c>
+      <c r="B152" s="13" t="s">
+        <v>338</v>
+      </c>
+      <c r="C152" s="14" t="s">
         <v>339</v>
-      </c>
-      <c r="B152" s="13" t="s">
-        <v>340</v>
-      </c>
-      <c r="C152" s="14" t="s">
-        <v>341</v>
       </c>
       <c r="D152" s="15" t="s">
         <v>25</v>
@@ -7262,13 +7256,13 @@
     </row>
     <row r="153" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A153" s="17" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="B153" s="18" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C153" s="19" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="D153" s="20" t="s">
         <v>25</v>
@@ -7288,13 +7282,13 @@
     </row>
     <row r="154" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A154" s="12" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B154" s="13" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C154" s="14" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="D154" s="15" t="s">
         <v>25</v>
@@ -7314,13 +7308,13 @@
     </row>
     <row r="155" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A155" s="17" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B155" s="18" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C155" s="19" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="D155" s="20" t="s">
         <v>25</v>
@@ -7340,13 +7334,13 @@
     </row>
     <row r="156" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A156" s="12" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B156" s="13" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C156" s="14" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="D156" s="15" t="s">
         <v>25</v>
@@ -7366,13 +7360,13 @@
     </row>
     <row r="157" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A157" s="17" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="B157" s="18" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C157" s="19" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="D157" s="20" t="s">
         <v>25</v>
@@ -7392,13 +7386,13 @@
     </row>
     <row r="158" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A158" s="12" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B158" s="13" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C158" s="14" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="D158" s="15" t="s">
         <v>25</v>
@@ -7418,13 +7412,13 @@
     </row>
     <row r="159" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A159" s="17" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="B159" s="18" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C159" s="19" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="D159" s="20" t="s">
         <v>25</v>
@@ -7444,13 +7438,13 @@
     </row>
     <row r="160" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A160" s="12" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="B160" s="13" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C160" s="14" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="D160" s="15" t="s">
         <v>25</v>
@@ -7470,13 +7464,13 @@
     </row>
     <row r="161" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A161" s="17" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B161" s="18" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C161" s="19" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="D161" s="20" t="s">
         <v>25</v>
@@ -7496,13 +7490,13 @@
     </row>
     <row r="162" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A162" s="12" t="s">
+        <v>358</v>
+      </c>
+      <c r="B162" s="13" t="s">
+        <v>359</v>
+      </c>
+      <c r="C162" s="14" t="s">
         <v>360</v>
-      </c>
-      <c r="B162" s="13" t="s">
-        <v>361</v>
-      </c>
-      <c r="C162" s="14" t="s">
-        <v>362</v>
       </c>
       <c r="D162" s="15" t="s">
         <v>25</v>
@@ -7522,13 +7516,13 @@
     </row>
     <row r="163" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A163" s="17" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B163" s="18" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C163" s="19" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="D163" s="20" t="s">
         <v>25</v>
@@ -7548,13 +7542,13 @@
     </row>
     <row r="164" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A164" s="12" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="B164" s="13" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C164" s="14" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="D164" s="15" t="s">
         <v>25</v>
@@ -7574,13 +7568,13 @@
     </row>
     <row r="165" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A165" s="17" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="B165" s="18" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C165" s="19" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="D165" s="20" t="s">
         <v>25</v>
@@ -7600,13 +7594,13 @@
     </row>
     <row r="166" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A166" s="12" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="B166" s="13" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C166" s="14" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="D166" s="15" t="s">
         <v>25</v>
@@ -7626,13 +7620,13 @@
     </row>
     <row r="167" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A167" s="17" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="B167" s="18" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C167" s="19" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="D167" s="20" t="s">
         <v>25</v>
@@ -7652,13 +7646,13 @@
     </row>
     <row r="168" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A168" s="12" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="B168" s="13" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C168" s="14" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="D168" s="15" t="s">
         <v>25</v>
@@ -7678,13 +7672,13 @@
     </row>
     <row r="169" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A169" s="17" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B169" s="18" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C169" s="19" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="D169" s="20" t="s">
         <v>25</v>
@@ -7704,13 +7698,13 @@
     </row>
     <row r="170" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A170" s="12" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B170" s="13" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C170" s="14" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="D170" s="15" t="s">
         <v>25</v>
@@ -7730,13 +7724,13 @@
     </row>
     <row r="171" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A171" s="17" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="B171" s="18" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C171" s="19" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="D171" s="20" t="s">
         <v>25</v>
@@ -7756,13 +7750,13 @@
     </row>
     <row r="172" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A172" s="12" t="s">
+        <v>379</v>
+      </c>
+      <c r="B172" s="13" t="s">
+        <v>380</v>
+      </c>
+      <c r="C172" s="14" t="s">
         <v>381</v>
-      </c>
-      <c r="B172" s="13" t="s">
-        <v>382</v>
-      </c>
-      <c r="C172" s="14" t="s">
-        <v>383</v>
       </c>
       <c r="D172" s="15" t="s">
         <v>25</v>
@@ -7782,13 +7776,13 @@
     </row>
     <row r="173" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A173" s="17" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="B173" s="18" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C173" s="19" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="D173" s="20" t="s">
         <v>25</v>
@@ -7808,13 +7802,13 @@
     </row>
     <row r="174" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A174" s="12" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="B174" s="13" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C174" s="14" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="D174" s="15" t="s">
         <v>25</v>
@@ -7834,13 +7828,13 @@
     </row>
     <row r="175" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A175" s="17" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="B175" s="18" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C175" s="19" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="D175" s="20" t="s">
         <v>25</v>
@@ -7860,13 +7854,13 @@
     </row>
     <row r="176" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A176" s="12" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="B176" s="13" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C176" s="14" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="D176" s="15" t="s">
         <v>25</v>
@@ -7886,13 +7880,13 @@
     </row>
     <row r="177" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A177" s="17" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="B177" s="18" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C177" s="19" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="D177" s="20" t="s">
         <v>25</v>
@@ -7912,13 +7906,13 @@
     </row>
     <row r="178" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A178" s="12" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="B178" s="13" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C178" s="14" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="D178" s="15" t="s">
         <v>25</v>
@@ -7938,13 +7932,13 @@
     </row>
     <row r="179" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A179" s="17" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="B179" s="18" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C179" s="19" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="D179" s="20" t="s">
         <v>25</v>
@@ -7964,13 +7958,13 @@
     </row>
     <row r="180" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A180" s="12" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="B180" s="13" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C180" s="14" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="D180" s="15" t="s">
         <v>25</v>
@@ -7990,13 +7984,13 @@
     </row>
     <row r="181" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A181" s="17" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="B181" s="18" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C181" s="19" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="D181" s="20" t="s">
         <v>25</v>
@@ -8016,13 +8010,13 @@
     </row>
     <row r="182" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A182" s="12" t="s">
+        <v>400</v>
+      </c>
+      <c r="B182" s="13" t="s">
+        <v>401</v>
+      </c>
+      <c r="C182" s="14" t="s">
         <v>402</v>
-      </c>
-      <c r="B182" s="13" t="s">
-        <v>403</v>
-      </c>
-      <c r="C182" s="14" t="s">
-        <v>404</v>
       </c>
       <c r="D182" s="15" t="s">
         <v>25</v>
@@ -8042,13 +8036,13 @@
     </row>
     <row r="183" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A183" s="17" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B183" s="18" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="C183" s="19" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="D183" s="20" t="s">
         <v>25</v>
@@ -8068,13 +8062,13 @@
     </row>
     <row r="184" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A184" s="12" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="B184" s="13" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="C184" s="14" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="D184" s="15" t="s">
         <v>25</v>
@@ -8094,13 +8088,13 @@
     </row>
     <row r="185" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A185" s="17" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="B185" s="18" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="C185" s="19" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="D185" s="20" t="s">
         <v>25</v>
@@ -8120,13 +8114,13 @@
     </row>
     <row r="186" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A186" s="12" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="B186" s="13" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="C186" s="14" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="D186" s="15" t="s">
         <v>25</v>
@@ -8146,13 +8140,13 @@
     </row>
     <row r="187" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A187" s="17" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="B187" s="18" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="C187" s="19" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="D187" s="20" t="s">
         <v>25</v>
@@ -8172,13 +8166,13 @@
     </row>
     <row r="188" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A188" s="12" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="B188" s="13" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="C188" s="14" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="D188" s="15" t="s">
         <v>25</v>
@@ -8198,13 +8192,13 @@
     </row>
     <row r="189" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A189" s="17" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="B189" s="18" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="C189" s="19" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="D189" s="20" t="s">
         <v>25</v>
@@ -8224,13 +8218,13 @@
     </row>
     <row r="190" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A190" s="12" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B190" s="13" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="C190" s="14" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="D190" s="15" t="s">
         <v>25</v>
@@ -8250,13 +8244,13 @@
     </row>
     <row r="191" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A191" s="17" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="B191" s="18" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="C191" s="19" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="D191" s="20" t="s">
         <v>25</v>
@@ -8276,13 +8270,13 @@
     </row>
     <row r="192" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A192" s="12" t="s">
+        <v>421</v>
+      </c>
+      <c r="B192" s="13" t="s">
+        <v>422</v>
+      </c>
+      <c r="C192" s="14" t="s">
         <v>423</v>
-      </c>
-      <c r="B192" s="13" t="s">
-        <v>424</v>
-      </c>
-      <c r="C192" s="14" t="s">
-        <v>425</v>
       </c>
       <c r="D192" s="15" t="s">
         <v>25</v>
@@ -8302,13 +8296,13 @@
     </row>
     <row r="193" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A193" s="17" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B193" s="18" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="C193" s="19" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="D193" s="20" t="s">
         <v>25</v>
@@ -8328,13 +8322,13 @@
     </row>
     <row r="194" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A194" s="12" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="B194" s="13" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="C194" s="14" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="D194" s="15" t="s">
         <v>25</v>
@@ -8354,13 +8348,13 @@
     </row>
     <row r="195" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A195" s="17" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="B195" s="18" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="C195" s="19" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="D195" s="20" t="s">
         <v>25</v>
@@ -8380,13 +8374,13 @@
     </row>
     <row r="196" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A196" s="12" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="B196" s="13" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="C196" s="14" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="D196" s="15" t="s">
         <v>25</v>
@@ -8406,13 +8400,13 @@
     </row>
     <row r="197" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A197" s="17" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="B197" s="18" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="C197" s="19" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="D197" s="20" t="s">
         <v>25</v>
@@ -8432,13 +8426,13 @@
     </row>
     <row r="198" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A198" s="12" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="B198" s="13" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="C198" s="14" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="D198" s="15" t="s">
         <v>25</v>
@@ -8458,13 +8452,13 @@
     </row>
     <row r="199" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A199" s="17" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="B199" s="18" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="C199" s="19" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="D199" s="20" t="s">
         <v>25</v>
@@ -8484,13 +8478,13 @@
     </row>
     <row r="200" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A200" s="12" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="B200" s="13" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="C200" s="14" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="D200" s="15" t="s">
         <v>25</v>
@@ -8510,13 +8504,13 @@
     </row>
     <row r="201" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A201" s="17" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="B201" s="18" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="C201" s="19" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="D201" s="20" t="s">
         <v>25</v>
@@ -8536,13 +8530,13 @@
     </row>
     <row r="202" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A202" s="12" t="s">
+        <v>442</v>
+      </c>
+      <c r="B202" s="13" t="s">
+        <v>443</v>
+      </c>
+      <c r="C202" s="14" t="s">
         <v>444</v>
-      </c>
-      <c r="B202" s="13" t="s">
-        <v>445</v>
-      </c>
-      <c r="C202" s="14" t="s">
-        <v>446</v>
       </c>
       <c r="D202" s="15" t="s">
         <v>25</v>
@@ -8562,13 +8556,13 @@
     </row>
     <row r="203" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A203" s="17" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="B203" s="18" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="C203" s="19" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="D203" s="20" t="s">
         <v>25</v>
@@ -8588,13 +8582,13 @@
     </row>
     <row r="204" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A204" s="12" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="B204" s="13" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="C204" s="14" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="D204" s="15" t="s">
         <v>25</v>
@@ -8614,13 +8608,13 @@
     </row>
     <row r="205" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A205" s="17" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="B205" s="18" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="C205" s="19" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="D205" s="20" t="s">
         <v>25</v>
@@ -8640,13 +8634,13 @@
     </row>
     <row r="206" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A206" s="12" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B206" s="13" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="C206" s="14" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="D206" s="15" t="s">
         <v>25</v>
@@ -8666,13 +8660,13 @@
     </row>
     <row r="207" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A207" s="17" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="B207" s="18" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="C207" s="19" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="D207" s="20" t="s">
         <v>25</v>
@@ -8692,13 +8686,13 @@
     </row>
     <row r="208" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A208" s="12" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="B208" s="13" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="C208" s="14" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="D208" s="15" t="s">
         <v>25</v>
@@ -8718,13 +8712,13 @@
     </row>
     <row r="209" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A209" s="17" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="B209" s="18" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="C209" s="19" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="D209" s="20" t="s">
         <v>25</v>
@@ -8744,13 +8738,13 @@
     </row>
     <row r="210" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A210" s="12" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="B210" s="13" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="C210" s="14" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="D210" s="15" t="s">
         <v>25</v>
@@ -8770,13 +8764,13 @@
     </row>
     <row r="211" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A211" s="17" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="B211" s="18" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="C211" s="19" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="D211" s="20" t="s">
         <v>25</v>
@@ -8796,13 +8790,13 @@
     </row>
     <row r="212" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A212" s="12" t="s">
+        <v>463</v>
+      </c>
+      <c r="B212" s="13" t="s">
+        <v>464</v>
+      </c>
+      <c r="C212" s="14" t="s">
         <v>465</v>
-      </c>
-      <c r="B212" s="13" t="s">
-        <v>466</v>
-      </c>
-      <c r="C212" s="14" t="s">
-        <v>467</v>
       </c>
       <c r="D212" s="15" t="s">
         <v>25</v>
@@ -8822,13 +8816,13 @@
     </row>
     <row r="213" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A213" s="17" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="B213" s="18" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="C213" s="19" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="D213" s="20" t="s">
         <v>25</v>
@@ -8848,13 +8842,13 @@
     </row>
     <row r="214" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A214" s="12" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="B214" s="13" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="C214" s="14" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="D214" s="15" t="s">
         <v>25</v>
@@ -8874,13 +8868,13 @@
     </row>
     <row r="215" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A215" s="17" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="B215" s="18" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="C215" s="19" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="D215" s="20" t="s">
         <v>25</v>
@@ -8900,13 +8894,13 @@
     </row>
     <row r="216" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A216" s="12" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="B216" s="13" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="C216" s="14" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="D216" s="15" t="s">
         <v>25</v>
@@ -8926,13 +8920,13 @@
     </row>
     <row r="217" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A217" s="17" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="B217" s="18" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="C217" s="19" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="D217" s="20" t="s">
         <v>25</v>
@@ -8952,13 +8946,13 @@
     </row>
     <row r="218" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A218" s="12" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="B218" s="13" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="C218" s="14" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D218" s="15" t="s">
         <v>25</v>
@@ -8978,13 +8972,13 @@
     </row>
     <row r="219" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A219" s="17" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="B219" s="18" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="C219" s="19" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="D219" s="20" t="s">
         <v>25</v>
@@ -9004,13 +8998,13 @@
     </row>
     <row r="220" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A220" s="12" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="B220" s="13" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="C220" s="14" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="D220" s="15" t="s">
         <v>25</v>
@@ -9030,13 +9024,13 @@
     </row>
     <row r="221" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A221" s="17" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="B221" s="18" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="C221" s="19" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="D221" s="20" t="s">
         <v>25</v>
@@ -9056,13 +9050,13 @@
     </row>
     <row r="222" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A222" s="12" t="s">
+        <v>484</v>
+      </c>
+      <c r="B222" s="13" t="s">
+        <v>485</v>
+      </c>
+      <c r="C222" s="14" t="s">
         <v>486</v>
-      </c>
-      <c r="B222" s="13" t="s">
-        <v>487</v>
-      </c>
-      <c r="C222" s="14" t="s">
-        <v>488</v>
       </c>
       <c r="D222" s="15" t="s">
         <v>25</v>
@@ -9082,13 +9076,13 @@
     </row>
     <row r="223" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A223" s="17" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="B223" s="18" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="C223" s="19" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="D223" s="20" t="s">
         <v>25</v>
@@ -9108,13 +9102,13 @@
     </row>
     <row r="224" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A224" s="12" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="B224" s="13" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="C224" s="14" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="D224" s="15" t="s">
         <v>25</v>
@@ -9134,13 +9128,13 @@
     </row>
     <row r="225" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A225" s="17" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="B225" s="18" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="C225" s="19" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="D225" s="20" t="s">
         <v>25</v>
@@ -9160,13 +9154,13 @@
     </row>
     <row r="226" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A226" s="12" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="B226" s="13" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="C226" s="14" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="D226" s="15" t="s">
         <v>25</v>
@@ -9186,13 +9180,13 @@
     </row>
     <row r="227" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A227" s="17" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="B227" s="18" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="C227" s="19" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="D227" s="20" t="s">
         <v>25</v>
@@ -9212,13 +9206,13 @@
     </row>
     <row r="228" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A228" s="12" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="B228" s="13" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="C228" s="14" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="D228" s="15" t="s">
         <v>25</v>
@@ -9238,13 +9232,13 @@
     </row>
     <row r="229" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A229" s="17" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="B229" s="18" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="C229" s="19" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="D229" s="20" t="s">
         <v>25</v>
@@ -9264,13 +9258,13 @@
     </row>
     <row r="230" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A230" s="12" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="B230" s="13" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="C230" s="14" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="D230" s="15" t="s">
         <v>25</v>
@@ -9290,13 +9284,13 @@
     </row>
     <row r="231" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A231" s="17" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="B231" s="18" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="C231" s="19" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="D231" s="20" t="s">
         <v>25</v>
@@ -9316,13 +9310,13 @@
     </row>
     <row r="232" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A232" s="12" t="s">
+        <v>505</v>
+      </c>
+      <c r="B232" s="13" t="s">
+        <v>506</v>
+      </c>
+      <c r="C232" s="14" t="s">
         <v>507</v>
-      </c>
-      <c r="B232" s="13" t="s">
-        <v>508</v>
-      </c>
-      <c r="C232" s="14" t="s">
-        <v>509</v>
       </c>
       <c r="D232" s="15" t="s">
         <v>25</v>
@@ -9342,13 +9336,13 @@
     </row>
     <row r="233" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A233" s="17" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B233" s="18" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="C233" s="19" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="D233" s="20" t="s">
         <v>25</v>
@@ -9368,13 +9362,13 @@
     </row>
     <row r="234" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A234" s="12" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="B234" s="13" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="C234" s="14" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="D234" s="15" t="s">
         <v>25</v>
@@ -9394,13 +9388,13 @@
     </row>
     <row r="235" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A235" s="17" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="B235" s="18" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="C235" s="19" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="D235" s="20" t="s">
         <v>25</v>
@@ -9420,13 +9414,13 @@
     </row>
     <row r="236" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A236" s="12" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="B236" s="13" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="C236" s="14" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="D236" s="15" t="s">
         <v>25</v>
@@ -9446,13 +9440,13 @@
     </row>
     <row r="237" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A237" s="17" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="B237" s="18" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="C237" s="19" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="D237" s="20" t="s">
         <v>25</v>
@@ -9472,13 +9466,13 @@
     </row>
     <row r="238" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A238" s="12" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="B238" s="13" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="C238" s="14" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="D238" s="15" t="s">
         <v>25</v>
@@ -9498,13 +9492,13 @@
     </row>
     <row r="239" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A239" s="17" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="B239" s="18" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="C239" s="19" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="D239" s="20" t="s">
         <v>25</v>
@@ -9524,13 +9518,13 @@
     </row>
     <row r="240" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A240" s="12" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="B240" s="13" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="C240" s="14" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="D240" s="15" t="s">
         <v>25</v>
@@ -9550,13 +9544,13 @@
     </row>
     <row r="241" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A241" s="17" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="B241" s="18" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="C241" s="19" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="D241" s="20" t="s">
         <v>25</v>
@@ -9576,13 +9570,13 @@
     </row>
     <row r="242" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A242" s="12" t="s">
+        <v>526</v>
+      </c>
+      <c r="B242" s="13" t="s">
+        <v>527</v>
+      </c>
+      <c r="C242" s="14" t="s">
         <v>528</v>
-      </c>
-      <c r="B242" s="13" t="s">
-        <v>529</v>
-      </c>
-      <c r="C242" s="14" t="s">
-        <v>530</v>
       </c>
       <c r="D242" s="15" t="s">
         <v>25</v>
@@ -9602,13 +9596,13 @@
     </row>
     <row r="243" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A243" s="17" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="B243" s="18" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="C243" s="19" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="D243" s="20" t="s">
         <v>25</v>
@@ -9628,13 +9622,13 @@
     </row>
     <row r="244" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A244" s="12" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="B244" s="13" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="C244" s="14" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="D244" s="15" t="s">
         <v>25</v>
@@ -9654,13 +9648,13 @@
     </row>
     <row r="245" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A245" s="17" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="B245" s="18" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="C245" s="19" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="D245" s="20" t="s">
         <v>25</v>
@@ -9680,13 +9674,13 @@
     </row>
     <row r="246" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A246" s="12" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="B246" s="13" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="C246" s="14" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="D246" s="15" t="s">
         <v>25</v>
@@ -9706,13 +9700,13 @@
     </row>
     <row r="247" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A247" s="17" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="B247" s="18" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="C247" s="19" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="D247" s="20" t="s">
         <v>25</v>
@@ -9732,13 +9726,13 @@
     </row>
     <row r="248" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A248" s="12" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="B248" s="13" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="C248" s="14" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="D248" s="15" t="s">
         <v>25</v>
@@ -9758,13 +9752,13 @@
     </row>
     <row r="249" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A249" s="17" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="B249" s="18" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="C249" s="19" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="D249" s="20" t="s">
         <v>25</v>
@@ -9784,13 +9778,13 @@
     </row>
     <row r="250" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A250" s="12" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="B250" s="13" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="C250" s="14" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="D250" s="15" t="s">
         <v>25</v>
@@ -9810,13 +9804,13 @@
     </row>
     <row r="251" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A251" s="17" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="B251" s="18" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="C251" s="19" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="D251" s="20" t="s">
         <v>25</v>
@@ -9836,13 +9830,13 @@
     </row>
     <row r="252" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A252" s="12" t="s">
+        <v>547</v>
+      </c>
+      <c r="B252" s="13" t="s">
+        <v>548</v>
+      </c>
+      <c r="C252" s="14" t="s">
         <v>549</v>
-      </c>
-      <c r="B252" s="13" t="s">
-        <v>550</v>
-      </c>
-      <c r="C252" s="14" t="s">
-        <v>551</v>
       </c>
       <c r="D252" s="15" t="s">
         <v>25</v>
@@ -9862,13 +9856,13 @@
     </row>
     <row r="253" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A253" s="17" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="B253" s="18" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="C253" s="19" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="D253" s="20" t="s">
         <v>25</v>
@@ -9888,13 +9882,13 @@
     </row>
     <row r="254" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A254" s="12" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="B254" s="13" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="C254" s="14" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="D254" s="15" t="s">
         <v>25</v>
@@ -9914,13 +9908,13 @@
     </row>
     <row r="255" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A255" s="17" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="B255" s="18" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="C255" s="19" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="D255" s="20" t="s">
         <v>25</v>
@@ -9940,13 +9934,13 @@
     </row>
     <row r="256" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A256" s="12" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="B256" s="13" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="C256" s="14" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="D256" s="15" t="s">
         <v>25</v>
@@ -9966,13 +9960,13 @@
     </row>
     <row r="257" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A257" s="17" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="B257" s="18" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="C257" s="19" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="D257" s="20" t="s">
         <v>25</v>
@@ -9992,13 +9986,13 @@
     </row>
     <row r="258" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A258" s="12" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="B258" s="13" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="C258" s="14" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="D258" s="15" t="s">
         <v>25</v>
@@ -10018,13 +10012,13 @@
     </row>
     <row r="259" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A259" s="17" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="B259" s="18" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="C259" s="19" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="D259" s="20" t="s">
         <v>25</v>
@@ -10044,13 +10038,13 @@
     </row>
     <row r="260" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A260" s="12" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="B260" s="13" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="C260" s="14" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="D260" s="15" t="s">
         <v>25</v>
@@ -10070,13 +10064,13 @@
     </row>
     <row r="261" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A261" s="17" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="B261" s="18" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="C261" s="19" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="D261" s="20" t="s">
         <v>25</v>
@@ -10096,13 +10090,13 @@
     </row>
     <row r="262" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A262" s="12" t="s">
+        <v>568</v>
+      </c>
+      <c r="B262" s="13" t="s">
+        <v>569</v>
+      </c>
+      <c r="C262" s="14" t="s">
         <v>570</v>
-      </c>
-      <c r="B262" s="13" t="s">
-        <v>571</v>
-      </c>
-      <c r="C262" s="14" t="s">
-        <v>572</v>
       </c>
       <c r="D262" s="15" t="s">
         <v>25</v>
@@ -10122,13 +10116,13 @@
     </row>
     <row r="263" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A263" s="17" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="B263" s="18" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="C263" s="19" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="D263" s="20" t="s">
         <v>25</v>
@@ -10148,13 +10142,13 @@
     </row>
     <row r="264" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A264" s="12" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="B264" s="13" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="C264" s="14" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="D264" s="15" t="s">
         <v>25</v>
@@ -10174,13 +10168,13 @@
     </row>
     <row r="265" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A265" s="17" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="B265" s="18" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="C265" s="19" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="D265" s="20" t="s">
         <v>25</v>
@@ -10200,13 +10194,13 @@
     </row>
     <row r="266" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A266" s="12" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="B266" s="13" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="C266" s="14" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="D266" s="15" t="s">
         <v>25</v>
@@ -10226,13 +10220,13 @@
     </row>
     <row r="267" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A267" s="17" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="B267" s="18" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="C267" s="19" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="D267" s="20" t="s">
         <v>25</v>
@@ -10252,13 +10246,13 @@
     </row>
     <row r="268" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A268" s="12" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="B268" s="13" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="C268" s="14" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="D268" s="15" t="s">
         <v>25</v>
@@ -10278,13 +10272,13 @@
     </row>
     <row r="269" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A269" s="17" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="B269" s="18" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="C269" s="19" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="D269" s="20" t="s">
         <v>25</v>
@@ -10304,13 +10298,13 @@
     </row>
     <row r="270" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A270" s="12" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="B270" s="13" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="C270" s="14" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="D270" s="15" t="s">
         <v>25</v>
@@ -10330,13 +10324,13 @@
     </row>
     <row r="271" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A271" s="17" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="B271" s="18" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="C271" s="19" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="D271" s="20" t="s">
         <v>25</v>
@@ -10356,13 +10350,13 @@
     </row>
     <row r="272" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A272" s="12" t="s">
+        <v>589</v>
+      </c>
+      <c r="B272" s="13" t="s">
+        <v>590</v>
+      </c>
+      <c r="C272" s="14" t="s">
         <v>591</v>
-      </c>
-      <c r="B272" s="13" t="s">
-        <v>592</v>
-      </c>
-      <c r="C272" s="14" t="s">
-        <v>593</v>
       </c>
       <c r="D272" s="15" t="s">
         <v>25</v>
@@ -10382,13 +10376,13 @@
     </row>
     <row r="273" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A273" s="17" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="B273" s="18" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="C273" s="19" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="D273" s="20" t="s">
         <v>25</v>
@@ -10408,13 +10402,13 @@
     </row>
     <row r="274" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A274" s="12" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="B274" s="13" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="C274" s="14" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="D274" s="15" t="s">
         <v>25</v>
@@ -10434,13 +10428,13 @@
     </row>
     <row r="275" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A275" s="17" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="B275" s="18" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="C275" s="19" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="D275" s="20" t="s">
         <v>25</v>
@@ -10460,13 +10454,13 @@
     </row>
     <row r="276" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A276" s="12" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="B276" s="13" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="C276" s="14" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="D276" s="15" t="s">
         <v>25</v>
@@ -10486,13 +10480,13 @@
     </row>
     <row r="277" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A277" s="17" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="B277" s="18" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="C277" s="19" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="D277" s="20" t="s">
         <v>25</v>
@@ -10512,13 +10506,13 @@
     </row>
     <row r="278" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A278" s="12" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="B278" s="13" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="C278" s="14" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="D278" s="15" t="s">
         <v>25</v>
@@ -10538,13 +10532,13 @@
     </row>
     <row r="279" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A279" s="17" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="B279" s="18" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="C279" s="19" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="D279" s="20" t="s">
         <v>25</v>
@@ -10564,13 +10558,13 @@
     </row>
     <row r="280" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A280" s="12" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="B280" s="13" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="C280" s="14" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="D280" s="15" t="s">
         <v>25</v>
@@ -10590,13 +10584,13 @@
     </row>
     <row r="281" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A281" s="17" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="B281" s="18" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="C281" s="19" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="D281" s="20" t="s">
         <v>25</v>
@@ -10616,13 +10610,13 @@
     </row>
     <row r="282" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A282" s="12" t="s">
+        <v>610</v>
+      </c>
+      <c r="B282" s="13" t="s">
+        <v>611</v>
+      </c>
+      <c r="C282" s="14" t="s">
         <v>612</v>
-      </c>
-      <c r="B282" s="13" t="s">
-        <v>613</v>
-      </c>
-      <c r="C282" s="14" t="s">
-        <v>614</v>
       </c>
       <c r="D282" s="15" t="s">
         <v>25</v>
@@ -10642,13 +10636,13 @@
     </row>
     <row r="283" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A283" s="17" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="B283" s="18" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="C283" s="19" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="D283" s="20" t="s">
         <v>25</v>
@@ -10668,13 +10662,13 @@
     </row>
     <row r="284" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A284" s="12" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="B284" s="13" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="C284" s="14" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="D284" s="15" t="s">
         <v>25</v>
@@ -10694,13 +10688,13 @@
     </row>
     <row r="285" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A285" s="17" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="B285" s="18" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="C285" s="19" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="D285" s="20" t="s">
         <v>25</v>
@@ -10720,13 +10714,13 @@
     </row>
     <row r="286" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A286" s="12" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="B286" s="13" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="C286" s="14" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="D286" s="15" t="s">
         <v>25</v>
@@ -10746,13 +10740,13 @@
     </row>
     <row r="287" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A287" s="17" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="B287" s="18" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="C287" s="19" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="D287" s="20" t="s">
         <v>25</v>
@@ -10772,13 +10766,13 @@
     </row>
     <row r="288" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A288" s="12" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="B288" s="13" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="C288" s="14" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="D288" s="15" t="s">
         <v>25</v>
@@ -10798,13 +10792,13 @@
     </row>
     <row r="289" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A289" s="17" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="B289" s="18" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="C289" s="19" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="D289" s="20" t="s">
         <v>25</v>
@@ -10824,13 +10818,13 @@
     </row>
     <row r="290" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A290" s="12" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="B290" s="13" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="C290" s="14" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="D290" s="15" t="s">
         <v>25</v>
@@ -10850,13 +10844,13 @@
     </row>
     <row r="291" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A291" s="17" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="B291" s="18" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="C291" s="19" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="D291" s="20" t="s">
         <v>25</v>
@@ -10876,13 +10870,13 @@
     </row>
     <row r="292" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A292" s="12" t="s">
+        <v>631</v>
+      </c>
+      <c r="B292" s="13" t="s">
+        <v>632</v>
+      </c>
+      <c r="C292" s="14" t="s">
         <v>633</v>
-      </c>
-      <c r="B292" s="13" t="s">
-        <v>634</v>
-      </c>
-      <c r="C292" s="14" t="s">
-        <v>635</v>
       </c>
       <c r="D292" s="15" t="s">
         <v>25</v>
@@ -10902,13 +10896,13 @@
     </row>
     <row r="293" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A293" s="17" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="B293" s="18" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="C293" s="19" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="D293" s="20" t="s">
         <v>25</v>
@@ -10928,13 +10922,13 @@
     </row>
     <row r="294" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A294" s="12" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="B294" s="13" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="C294" s="14" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="D294" s="15" t="s">
         <v>25</v>
@@ -10954,13 +10948,13 @@
     </row>
     <row r="295" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A295" s="17" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="B295" s="18" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="C295" s="19" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="D295" s="20" t="s">
         <v>25</v>
@@ -10980,13 +10974,13 @@
     </row>
     <row r="296" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A296" s="12" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="B296" s="13" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="C296" s="14" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="D296" s="15" t="s">
         <v>25</v>
@@ -11006,13 +11000,13 @@
     </row>
     <row r="297" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A297" s="17" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B297" s="18" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="C297" s="19" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="D297" s="20" t="s">
         <v>25</v>
@@ -11032,13 +11026,13 @@
     </row>
     <row r="298" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A298" s="12" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="B298" s="13" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="C298" s="14" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="D298" s="15" t="s">
         <v>25</v>
@@ -11058,13 +11052,13 @@
     </row>
     <row r="299" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A299" s="17" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="B299" s="18" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="C299" s="19" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="D299" s="20" t="s">
         <v>25</v>
@@ -11084,13 +11078,13 @@
     </row>
     <row r="300" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A300" s="12" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="B300" s="13" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="C300" s="14" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="D300" s="15" t="s">
         <v>25</v>
@@ -11110,13 +11104,13 @@
     </row>
     <row r="301" ht="24" customHeight="1" spans="1:8" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A301" s="17" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="B301" s="18" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="C301" s="19" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="D301" s="20" t="s">
         <v>25</v>
@@ -11157,33 +11151,33 @@
         <v>16</v>
       </c>
       <c r="B1" s="21" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="C1" s="21" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="D1" s="21" t="s">
         <v>17</v>
       </c>
       <c r="E1" s="21" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:5" s="22" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="22" t="s">
+        <v>655</v>
+      </c>
+      <c r="B2" s="22" t="s">
+        <v>656</v>
+      </c>
+      <c r="C2" s="22" t="s">
         <v>657</v>
       </c>
-      <c r="B2" s="22" t="s">
+      <c r="D2" s="22" t="s">
         <v>658</v>
       </c>
-      <c r="C2" s="22" t="s">
+      <c r="E2" s="22" t="s">
         <v>659</v>
-      </c>
-      <c r="D2" s="22" t="s">
-        <v>660</v>
-      </c>
-      <c r="E2" s="22" t="s">
-        <v>661</v>
       </c>
     </row>
   </sheetData>
@@ -11206,19 +11200,19 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="23" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="B1" s="23" t="s">
         <v>16</v>
       </c>
       <c r="C1" s="23" t="s">
+        <v>661</v>
+      </c>
+      <c r="D1" s="23" t="s">
+        <v>662</v>
+      </c>
+      <c r="E1" s="23" t="s">
         <v>663</v>
-      </c>
-      <c r="D1" s="23" t="s">
-        <v>664</v>
-      </c>
-      <c r="E1" s="23" t="s">
-        <v>665</v>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11226,16 +11220,16 @@
         <v>27</v>
       </c>
       <c r="B2" s="24" t="s">
+        <v>664</v>
+      </c>
+      <c r="C2" s="24" t="s">
+        <v>665</v>
+      </c>
+      <c r="D2" s="25" t="s">
         <v>666</v>
       </c>
-      <c r="C2" s="24" t="s">
+      <c r="E2" s="24" t="s">
         <v>667</v>
-      </c>
-      <c r="D2" s="25" t="s">
-        <v>668</v>
-      </c>
-      <c r="E2" s="24" t="s">
-        <v>669</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11243,16 +11237,16 @@
         <v>27</v>
       </c>
       <c r="B3" s="26" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="C3" s="26" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="D3" s="27" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="E3" s="26" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11260,16 +11254,16 @@
         <v>27</v>
       </c>
       <c r="B4" s="24" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="C4" s="24" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="D4" s="25" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="E4" s="24" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11277,16 +11271,16 @@
         <v>27</v>
       </c>
       <c r="B5" s="26" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="C5" s="26" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="D5" s="27" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="E5" s="26" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11294,16 +11288,16 @@
         <v>27</v>
       </c>
       <c r="B6" s="24" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="C6" s="24" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="D6" s="25" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="E6" s="24" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11311,16 +11305,16 @@
         <v>27</v>
       </c>
       <c r="B7" s="26" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="C7" s="26" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="D7" s="27" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="E7" s="26" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11328,16 +11322,16 @@
         <v>27</v>
       </c>
       <c r="B8" s="24" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="C8" s="24" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="D8" s="25" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="E8" s="24" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11345,16 +11339,16 @@
         <v>27</v>
       </c>
       <c r="B9" s="26" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="C9" s="26" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="D9" s="27" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="E9" s="26" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11362,16 +11356,16 @@
         <v>27</v>
       </c>
       <c r="B10" s="24" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="C10" s="24" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="D10" s="25" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="E10" s="24" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11379,16 +11373,16 @@
         <v>27</v>
       </c>
       <c r="B11" s="26" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="C11" s="26" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="D11" s="27" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="E11" s="26" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11396,16 +11390,16 @@
         <v>27</v>
       </c>
       <c r="B12" s="24" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="C12" s="24" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="D12" s="25" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="E12" s="24" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11413,16 +11407,16 @@
         <v>27</v>
       </c>
       <c r="B13" s="26" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="C13" s="26" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="D13" s="27" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="E13" s="26" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11430,16 +11424,16 @@
         <v>27</v>
       </c>
       <c r="B14" s="24" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="C14" s="24" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="D14" s="25" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="E14" s="24" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11447,16 +11441,16 @@
         <v>27</v>
       </c>
       <c r="B15" s="26" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="C15" s="26" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="D15" s="27" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="E15" s="26" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11464,16 +11458,16 @@
         <v>27</v>
       </c>
       <c r="B16" s="24" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="C16" s="24" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="D16" s="25" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="E16" s="24" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11481,16 +11475,16 @@
         <v>27</v>
       </c>
       <c r="B17" s="26" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="C17" s="26" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="D17" s="27" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="E17" s="26" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11498,16 +11492,16 @@
         <v>27</v>
       </c>
       <c r="B18" s="24" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="C18" s="24" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="D18" s="25" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="E18" s="24" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11515,16 +11509,16 @@
         <v>27</v>
       </c>
       <c r="B19" s="26" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="C19" s="26" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="D19" s="27" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="E19" s="26" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11532,16 +11526,16 @@
         <v>27</v>
       </c>
       <c r="B20" s="24" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="C20" s="24" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="D20" s="25" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="E20" s="24" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11549,16 +11543,16 @@
         <v>27</v>
       </c>
       <c r="B21" s="26" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="C21" s="26" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="D21" s="27" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="E21" s="26" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
     </row>
     <row r="22" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11566,16 +11560,16 @@
         <v>27</v>
       </c>
       <c r="B22" s="24" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="C22" s="24" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="D22" s="25" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="E22" s="24" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
     </row>
     <row r="23" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11583,16 +11577,16 @@
         <v>27</v>
       </c>
       <c r="B23" s="26" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="C23" s="26" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="D23" s="27" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="E23" s="26" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11600,16 +11594,16 @@
         <v>27</v>
       </c>
       <c r="B24" s="24" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="C24" s="24" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="D24" s="25" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="E24" s="24" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
     </row>
     <row r="25" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11617,16 +11611,16 @@
         <v>27</v>
       </c>
       <c r="B25" s="26" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="C25" s="26" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="D25" s="27" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="E25" s="26" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
     </row>
     <row r="26" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11634,16 +11628,16 @@
         <v>27</v>
       </c>
       <c r="B26" s="24" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="C26" s="24" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="D26" s="25" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="E26" s="24" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
     </row>
     <row r="27" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11651,16 +11645,16 @@
         <v>27</v>
       </c>
       <c r="B27" s="26" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="C27" s="26" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="D27" s="27" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="E27" s="26" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11668,16 +11662,16 @@
         <v>27</v>
       </c>
       <c r="B28" s="24" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="C28" s="24" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="D28" s="25" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="E28" s="24" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
     </row>
     <row r="29" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11685,16 +11679,16 @@
         <v>27</v>
       </c>
       <c r="B29" s="26" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="C29" s="26" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="D29" s="27" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="E29" s="26" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
     </row>
     <row r="30" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11702,16 +11696,16 @@
         <v>27</v>
       </c>
       <c r="B30" s="24" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="C30" s="24" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="D30" s="25" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="E30" s="24" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
     </row>
     <row r="31" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11719,16 +11713,16 @@
         <v>27</v>
       </c>
       <c r="B31" s="26" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="C31" s="26" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="D31" s="27" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="E31" s="26" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
     </row>
     <row r="32" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11736,16 +11730,16 @@
         <v>27</v>
       </c>
       <c r="B32" s="24" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="C32" s="24" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="D32" s="25" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="E32" s="24" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
     </row>
     <row r="33" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11753,16 +11747,16 @@
         <v>27</v>
       </c>
       <c r="B33" s="26" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="C33" s="26" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="D33" s="27" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="E33" s="26" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
     </row>
     <row r="34" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11770,16 +11764,16 @@
         <v>27</v>
       </c>
       <c r="B34" s="24" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="C34" s="24" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="D34" s="25" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="E34" s="24" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
     </row>
     <row r="35" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11787,16 +11781,16 @@
         <v>27</v>
       </c>
       <c r="B35" s="26" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="C35" s="26" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="D35" s="27" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="E35" s="26" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
     </row>
     <row r="36" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11804,16 +11798,16 @@
         <v>27</v>
       </c>
       <c r="B36" s="24" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="C36" s="24" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="D36" s="25" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="E36" s="24" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
     </row>
     <row r="37" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11821,16 +11815,16 @@
         <v>27</v>
       </c>
       <c r="B37" s="26" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="C37" s="26" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="D37" s="27" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="E37" s="26" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
     </row>
     <row r="38" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11838,16 +11832,16 @@
         <v>27</v>
       </c>
       <c r="B38" s="24" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="C38" s="24" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="D38" s="25" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="E38" s="24" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
     </row>
     <row r="39" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11855,16 +11849,16 @@
         <v>27</v>
       </c>
       <c r="B39" s="26" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="C39" s="26" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="D39" s="27" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="E39" s="26" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
     </row>
     <row r="40" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11872,16 +11866,16 @@
         <v>27</v>
       </c>
       <c r="B40" s="24" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="C40" s="24" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="D40" s="25" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="E40" s="24" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
     </row>
     <row r="41" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11889,16 +11883,16 @@
         <v>27</v>
       </c>
       <c r="B41" s="26" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="C41" s="26" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="D41" s="27" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="E41" s="26" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
     </row>
     <row r="42" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11906,16 +11900,16 @@
         <v>27</v>
       </c>
       <c r="B42" s="24" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="C42" s="24" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="D42" s="25" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="E42" s="24" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
     </row>
     <row r="43" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11923,16 +11917,16 @@
         <v>27</v>
       </c>
       <c r="B43" s="26" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="C43" s="26" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="D43" s="27" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="E43" s="26" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
     </row>
     <row r="44" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11940,16 +11934,16 @@
         <v>27</v>
       </c>
       <c r="B44" s="24" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="C44" s="24" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="D44" s="25" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="E44" s="24" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
     </row>
     <row r="45" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11957,16 +11951,16 @@
         <v>27</v>
       </c>
       <c r="B45" s="26" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="C45" s="26" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="D45" s="27" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="E45" s="26" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
     </row>
     <row r="46" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11974,16 +11968,16 @@
         <v>27</v>
       </c>
       <c r="B46" s="24" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="C46" s="24" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="D46" s="25" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="E46" s="24" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
     </row>
     <row r="47" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -11991,16 +11985,16 @@
         <v>27</v>
       </c>
       <c r="B47" s="26" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="C47" s="26" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="D47" s="27" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="E47" s="26" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
     </row>
     <row r="48" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12008,16 +12002,16 @@
         <v>27</v>
       </c>
       <c r="B48" s="24" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="C48" s="24" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="D48" s="25" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="E48" s="24" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
     </row>
     <row r="49" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12025,16 +12019,16 @@
         <v>27</v>
       </c>
       <c r="B49" s="26" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="C49" s="26" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="D49" s="27" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="E49" s="26" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
     </row>
     <row r="50" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12042,16 +12036,16 @@
         <v>27</v>
       </c>
       <c r="B50" s="24" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="C50" s="24" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="D50" s="25" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="E50" s="24" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
     </row>
     <row r="51" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12059,16 +12053,16 @@
         <v>27</v>
       </c>
       <c r="B51" s="26" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="C51" s="26" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="D51" s="27" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="E51" s="26" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
     </row>
     <row r="52" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12076,16 +12070,16 @@
         <v>27</v>
       </c>
       <c r="B52" s="24" t="s">
+        <v>766</v>
+      </c>
+      <c r="C52" s="24" t="s">
+        <v>767</v>
+      </c>
+      <c r="D52" s="25" t="s">
+        <v>666</v>
+      </c>
+      <c r="E52" s="24" t="s">
         <v>768</v>
-      </c>
-      <c r="C52" s="24" t="s">
-        <v>769</v>
-      </c>
-      <c r="D52" s="25" t="s">
-        <v>668</v>
-      </c>
-      <c r="E52" s="24" t="s">
-        <v>770</v>
       </c>
     </row>
     <row r="53" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12093,16 +12087,16 @@
         <v>27</v>
       </c>
       <c r="B53" s="26" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="C53" s="26" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="D53" s="27" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="E53" s="26" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
     </row>
     <row r="54" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12110,16 +12104,16 @@
         <v>27</v>
       </c>
       <c r="B54" s="24" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="C54" s="24" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="D54" s="25" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="E54" s="24" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
     </row>
     <row r="55" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12127,16 +12121,16 @@
         <v>27</v>
       </c>
       <c r="B55" s="26" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="C55" s="26" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="D55" s="27" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="E55" s="26" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
     </row>
     <row r="56" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12144,16 +12138,16 @@
         <v>27</v>
       </c>
       <c r="B56" s="24" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="C56" s="24" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="D56" s="25" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="E56" s="24" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
     </row>
     <row r="57" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12161,16 +12155,16 @@
         <v>27</v>
       </c>
       <c r="B57" s="26" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="C57" s="26" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="D57" s="27" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="E57" s="26" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
     </row>
     <row r="58" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12178,16 +12172,16 @@
         <v>27</v>
       </c>
       <c r="B58" s="24" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="C58" s="24" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="D58" s="25" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="E58" s="24" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
     </row>
     <row r="59" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12195,16 +12189,16 @@
         <v>27</v>
       </c>
       <c r="B59" s="26" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="C59" s="26" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="D59" s="27" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="E59" s="26" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
     </row>
     <row r="60" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12212,16 +12206,16 @@
         <v>27</v>
       </c>
       <c r="B60" s="24" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="C60" s="24" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="D60" s="25" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="E60" s="24" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
     </row>
     <row r="61" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12229,16 +12223,16 @@
         <v>27</v>
       </c>
       <c r="B61" s="26" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="C61" s="26" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="D61" s="27" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="E61" s="26" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
     </row>
     <row r="62" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12246,16 +12240,16 @@
         <v>27</v>
       </c>
       <c r="B62" s="24" t="s">
+        <v>787</v>
+      </c>
+      <c r="C62" s="24" t="s">
+        <v>788</v>
+      </c>
+      <c r="D62" s="25" t="s">
+        <v>666</v>
+      </c>
+      <c r="E62" s="24" t="s">
         <v>789</v>
-      </c>
-      <c r="C62" s="24" t="s">
-        <v>790</v>
-      </c>
-      <c r="D62" s="25" t="s">
-        <v>668</v>
-      </c>
-      <c r="E62" s="24" t="s">
-        <v>791</v>
       </c>
     </row>
     <row r="63" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12263,16 +12257,16 @@
         <v>27</v>
       </c>
       <c r="B63" s="26" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="C63" s="26" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="D63" s="27" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="E63" s="26" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
     </row>
     <row r="64" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12280,16 +12274,16 @@
         <v>27</v>
       </c>
       <c r="B64" s="24" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="C64" s="24" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="D64" s="25" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="E64" s="24" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
     </row>
     <row r="65" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12297,16 +12291,16 @@
         <v>27</v>
       </c>
       <c r="B65" s="26" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="C65" s="26" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="D65" s="27" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="E65" s="26" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
     </row>
     <row r="66" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12314,16 +12308,16 @@
         <v>27</v>
       </c>
       <c r="B66" s="24" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="C66" s="24" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="D66" s="25" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="E66" s="24" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
     </row>
     <row r="67" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12331,16 +12325,16 @@
         <v>27</v>
       </c>
       <c r="B67" s="26" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="C67" s="26" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="D67" s="27" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="E67" s="26" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
     </row>
     <row r="68" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12348,16 +12342,16 @@
         <v>27</v>
       </c>
       <c r="B68" s="24" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="C68" s="24" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="D68" s="25" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="E68" s="24" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
     </row>
     <row r="69" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12365,16 +12359,16 @@
         <v>27</v>
       </c>
       <c r="B69" s="26" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="C69" s="26" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="D69" s="27" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="E69" s="26" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
     </row>
     <row r="70" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12382,16 +12376,16 @@
         <v>27</v>
       </c>
       <c r="B70" s="24" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="C70" s="24" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="D70" s="25" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="E70" s="24" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
     </row>
     <row r="71" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12399,16 +12393,16 @@
         <v>27</v>
       </c>
       <c r="B71" s="26" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="C71" s="26" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="D71" s="27" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="E71" s="26" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
     </row>
     <row r="72" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12416,16 +12410,16 @@
         <v>27</v>
       </c>
       <c r="B72" s="24" t="s">
+        <v>808</v>
+      </c>
+      <c r="C72" s="24" t="s">
+        <v>809</v>
+      </c>
+      <c r="D72" s="25" t="s">
+        <v>666</v>
+      </c>
+      <c r="E72" s="24" t="s">
         <v>810</v>
-      </c>
-      <c r="C72" s="24" t="s">
-        <v>811</v>
-      </c>
-      <c r="D72" s="25" t="s">
-        <v>668</v>
-      </c>
-      <c r="E72" s="24" t="s">
-        <v>812</v>
       </c>
     </row>
     <row r="73" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12433,16 +12427,16 @@
         <v>27</v>
       </c>
       <c r="B73" s="26" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="C73" s="26" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
       <c r="D73" s="27" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="E73" s="26" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
     </row>
     <row r="74" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12450,16 +12444,16 @@
         <v>27</v>
       </c>
       <c r="B74" s="24" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="C74" s="24" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="D74" s="25" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="E74" s="24" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
     </row>
     <row r="75" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12467,16 +12461,16 @@
         <v>27</v>
       </c>
       <c r="B75" s="26" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="C75" s="26" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="D75" s="27" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="E75" s="26" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
     </row>
     <row r="76" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12484,16 +12478,16 @@
         <v>27</v>
       </c>
       <c r="B76" s="24" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="C76" s="24" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="D76" s="25" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="E76" s="24" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
     </row>
     <row r="77" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12501,16 +12495,16 @@
         <v>27</v>
       </c>
       <c r="B77" s="26" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="C77" s="26" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="D77" s="27" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="E77" s="26" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
     </row>
     <row r="78" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12518,16 +12512,16 @@
         <v>27</v>
       </c>
       <c r="B78" s="24" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="C78" s="24" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="D78" s="25" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="E78" s="24" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
     </row>
     <row r="79" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12535,16 +12529,16 @@
         <v>27</v>
       </c>
       <c r="B79" s="26" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="C79" s="26" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="D79" s="27" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="E79" s="26" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
     </row>
     <row r="80" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12552,16 +12546,16 @@
         <v>27</v>
       </c>
       <c r="B80" s="24" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="C80" s="24" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="D80" s="25" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="E80" s="24" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
     </row>
     <row r="81" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12569,16 +12563,16 @@
         <v>27</v>
       </c>
       <c r="B81" s="26" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="C81" s="26" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="D81" s="27" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="E81" s="26" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
     </row>
     <row r="82" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12586,16 +12580,16 @@
         <v>27</v>
       </c>
       <c r="B82" s="24" t="s">
+        <v>829</v>
+      </c>
+      <c r="C82" s="24" t="s">
+        <v>830</v>
+      </c>
+      <c r="D82" s="25" t="s">
+        <v>666</v>
+      </c>
+      <c r="E82" s="24" t="s">
         <v>831</v>
-      </c>
-      <c r="C82" s="24" t="s">
-        <v>832</v>
-      </c>
-      <c r="D82" s="25" t="s">
-        <v>668</v>
-      </c>
-      <c r="E82" s="24" t="s">
-        <v>833</v>
       </c>
     </row>
     <row r="83" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12603,16 +12597,16 @@
         <v>27</v>
       </c>
       <c r="B83" s="26" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="C83" s="26" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="D83" s="27" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="E83" s="26" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
     </row>
     <row r="84" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12620,16 +12614,16 @@
         <v>27</v>
       </c>
       <c r="B84" s="24" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="C84" s="24" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="D84" s="25" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="E84" s="24" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
     </row>
     <row r="85" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12637,16 +12631,16 @@
         <v>27</v>
       </c>
       <c r="B85" s="26" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="C85" s="26" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="D85" s="27" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="E85" s="26" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
     </row>
     <row r="86" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12654,16 +12648,16 @@
         <v>27</v>
       </c>
       <c r="B86" s="24" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="C86" s="24" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="D86" s="25" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="E86" s="24" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
     </row>
     <row r="87" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12671,16 +12665,16 @@
         <v>27</v>
       </c>
       <c r="B87" s="26" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="C87" s="26" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="D87" s="27" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="E87" s="26" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
     </row>
     <row r="88" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12688,16 +12682,16 @@
         <v>27</v>
       </c>
       <c r="B88" s="24" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="C88" s="24" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="D88" s="25" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="E88" s="24" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
     </row>
     <row r="89" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12705,16 +12699,16 @@
         <v>27</v>
       </c>
       <c r="B89" s="26" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="C89" s="26" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="D89" s="27" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="E89" s="26" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
     </row>
     <row r="90" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12722,16 +12716,16 @@
         <v>27</v>
       </c>
       <c r="B90" s="24" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="C90" s="24" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="D90" s="25" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="E90" s="24" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
     </row>
     <row r="91" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -12739,16 +12733,16 @@
         <v>27</v>
       </c>
       <c r="B91" s="26" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
       <c r="C91" s="26" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
       <c r="D91" s="27" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="E91" s="26" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
     </row>
   </sheetData>
